--- a/Facilities.xlsx
+++ b/Facilities.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chinedu\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chinedu\Documents\GitHub\SOH-TRACKER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A20402E-7B7D-4F82-BDC6-BD099B93BA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2326E0C5-CB43-4317-8442-FCB3AFF915C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{894FD31D-B550-4319-A669-590A5406D934}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$372</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="764">
   <si>
     <t>Cluster</t>
   </si>
@@ -1230,6 +1233,1104 @@
   </si>
   <si>
     <t>Facility</t>
+  </si>
+  <si>
+    <t>NewDPT Orgunitid</t>
+  </si>
+  <si>
+    <t>Xk6KqKm7I1X</t>
+  </si>
+  <si>
+    <t>x6pnr8aUczc</t>
+  </si>
+  <si>
+    <t>f0W3b5pgsEq</t>
+  </si>
+  <si>
+    <t>WFila0TV02D</t>
+  </si>
+  <si>
+    <t>OxGTCa7PYrK</t>
+  </si>
+  <si>
+    <t>LbpZJufflmj</t>
+  </si>
+  <si>
+    <t>rAZZTN3NPbn</t>
+  </si>
+  <si>
+    <t>wOuUTDESozC</t>
+  </si>
+  <si>
+    <t>FtX5bCgth2c</t>
+  </si>
+  <si>
+    <t>QppIbUI9E92</t>
+  </si>
+  <si>
+    <t>tkCscwbaxNn</t>
+  </si>
+  <si>
+    <t>msvy1BMNG4T</t>
+  </si>
+  <si>
+    <t>xknfQ0UuSCR</t>
+  </si>
+  <si>
+    <t>s6XbPR3OegF</t>
+  </si>
+  <si>
+    <t>iEDgEzot3LB</t>
+  </si>
+  <si>
+    <t>H23GZWyRJNM</t>
+  </si>
+  <si>
+    <t>LKC6ntITSri</t>
+  </si>
+  <si>
+    <t>cHTHLQECBHb</t>
+  </si>
+  <si>
+    <t>w949T8DW7L2</t>
+  </si>
+  <si>
+    <t>f3qpgjf4fdc</t>
+  </si>
+  <si>
+    <t>BkHB5iIj0jE</t>
+  </si>
+  <si>
+    <t>ROhcChFLRHB</t>
+  </si>
+  <si>
+    <t>dDlGu8ragLX</t>
+  </si>
+  <si>
+    <t>wCxRMCfanmR</t>
+  </si>
+  <si>
+    <t>kcrAQzJEwGo</t>
+  </si>
+  <si>
+    <t>kadaoTuzzZB</t>
+  </si>
+  <si>
+    <t>t1WtaKu0BW8</t>
+  </si>
+  <si>
+    <t>gQq1bJCmyJS</t>
+  </si>
+  <si>
+    <t>g5Psu7erWCF</t>
+  </si>
+  <si>
+    <t>eGQQItC0MTW</t>
+  </si>
+  <si>
+    <t>Q689jAJI3Js</t>
+  </si>
+  <si>
+    <t>SZnl4IYKQLr</t>
+  </si>
+  <si>
+    <t>QcYZBqmqjYM</t>
+  </si>
+  <si>
+    <t>ZeAWlKmmHD6</t>
+  </si>
+  <si>
+    <t>tFd03cyPnIc</t>
+  </si>
+  <si>
+    <t>gDlP9E1MSLs</t>
+  </si>
+  <si>
+    <t>pcx8dqfvTNf</t>
+  </si>
+  <si>
+    <t>OIYR8MJMfZQ</t>
+  </si>
+  <si>
+    <t>EOvgMBtqofN</t>
+  </si>
+  <si>
+    <t>M3ZQaDW7UpR</t>
+  </si>
+  <si>
+    <t>xkpH2hszXMe</t>
+  </si>
+  <si>
+    <t>lXc0A4lYNzR</t>
+  </si>
+  <si>
+    <t>fU5nWtR42LW</t>
+  </si>
+  <si>
+    <t>s9QLxc3XNNt</t>
+  </si>
+  <si>
+    <t>we90AXVrhUv</t>
+  </si>
+  <si>
+    <t>PzbKulSKORy</t>
+  </si>
+  <si>
+    <t>PvDpVr5oSIP</t>
+  </si>
+  <si>
+    <t>QpDemAvM3Tf</t>
+  </si>
+  <si>
+    <t>EoeDzJ1FUKN</t>
+  </si>
+  <si>
+    <t>V0K20ejw5vr</t>
+  </si>
+  <si>
+    <t>hInawYnNUmI</t>
+  </si>
+  <si>
+    <t>HgxxN5GZv8Y</t>
+  </si>
+  <si>
+    <t>TNwOSX6UfCW</t>
+  </si>
+  <si>
+    <t>JnbNLi29aZL</t>
+  </si>
+  <si>
+    <t>DasDyIPK8jQ</t>
+  </si>
+  <si>
+    <t>gjvb2mcuOZZ</t>
+  </si>
+  <si>
+    <t>A6L3DXI7vu8</t>
+  </si>
+  <si>
+    <t>lo2x8EF5rhM</t>
+  </si>
+  <si>
+    <t>LCWjvz5dOlP</t>
+  </si>
+  <si>
+    <t>cx15guOPxbO</t>
+  </si>
+  <si>
+    <t>inCBJmF4JFt</t>
+  </si>
+  <si>
+    <t>ZYAnILVr8hO</t>
+  </si>
+  <si>
+    <t>B225kuLbUgG</t>
+  </si>
+  <si>
+    <t>QakabWqKtoZ</t>
+  </si>
+  <si>
+    <t>RIYmPUENtbn</t>
+  </si>
+  <si>
+    <t>mKYIhwM6HUb</t>
+  </si>
+  <si>
+    <t>Lc0UxCUN8HR</t>
+  </si>
+  <si>
+    <t>D2THA1qt3d0</t>
+  </si>
+  <si>
+    <t>GbE0t7bjJnD</t>
+  </si>
+  <si>
+    <t>V8OKshaayl3</t>
+  </si>
+  <si>
+    <t>BFoGpferx8t</t>
+  </si>
+  <si>
+    <t>Kw5uIY91GTt</t>
+  </si>
+  <si>
+    <t>jEvQxNUAX4X</t>
+  </si>
+  <si>
+    <t>VbYKP326qwm</t>
+  </si>
+  <si>
+    <t>qtDvX43LURH</t>
+  </si>
+  <si>
+    <t>afVyYoFxrMX</t>
+  </si>
+  <si>
+    <t>glt0a9JC4VC</t>
+  </si>
+  <si>
+    <t>ulyCfZ5PUNZ</t>
+  </si>
+  <si>
+    <t>x8kegIarjSt</t>
+  </si>
+  <si>
+    <t>kIt9h1ZjQfF</t>
+  </si>
+  <si>
+    <t>GRJ0TfOtuBq</t>
+  </si>
+  <si>
+    <t>fDMBrV8yYvC</t>
+  </si>
+  <si>
+    <t>HqwDi1gXzB7</t>
+  </si>
+  <si>
+    <t>uuowEK9WsHV</t>
+  </si>
+  <si>
+    <t>zhMuFPbxUZS</t>
+  </si>
+  <si>
+    <t>Burn2fP7Vah</t>
+  </si>
+  <si>
+    <t>VW6oZN1jKMg</t>
+  </si>
+  <si>
+    <t>JNAiwnKB4ks</t>
+  </si>
+  <si>
+    <t>YzuXkd7MRFN</t>
+  </si>
+  <si>
+    <t>Jy1QamYI1bH</t>
+  </si>
+  <si>
+    <t>Csj8K86dI08</t>
+  </si>
+  <si>
+    <t>OMnxQFcPQue</t>
+  </si>
+  <si>
+    <t>hNfDUCUydTq</t>
+  </si>
+  <si>
+    <t>FTq8s8aeOR6</t>
+  </si>
+  <si>
+    <t>W4QQK1UMCbp</t>
+  </si>
+  <si>
+    <t>tw3So15hy11</t>
+  </si>
+  <si>
+    <t>MSkfPHFQxNn</t>
+  </si>
+  <si>
+    <t>bcpqdvfnctU</t>
+  </si>
+  <si>
+    <t>XG0hzB6FVrw</t>
+  </si>
+  <si>
+    <t>FSc9ugUcPXH</t>
+  </si>
+  <si>
+    <t>l8PcRaxktWI</t>
+  </si>
+  <si>
+    <t>M5GJmiCIWB7</t>
+  </si>
+  <si>
+    <t>GLMYeYnzEc9</t>
+  </si>
+  <si>
+    <t>MbKTJ6Rc6p8</t>
+  </si>
+  <si>
+    <t>ahxmPgVJ25m</t>
+  </si>
+  <si>
+    <t>D4TgYWg2wJM</t>
+  </si>
+  <si>
+    <t>QylicvgIoIH</t>
+  </si>
+  <si>
+    <t>XHjCK9WeTf8</t>
+  </si>
+  <si>
+    <t>HFpag6rQaIX</t>
+  </si>
+  <si>
+    <t>ekC51D8K5Cr</t>
+  </si>
+  <si>
+    <t>Ha1Uxfwnmwq</t>
+  </si>
+  <si>
+    <t>EPbgU2jpfSf</t>
+  </si>
+  <si>
+    <t>MjezVROb1oj</t>
+  </si>
+  <si>
+    <t>M88f5KX9VzP</t>
+  </si>
+  <si>
+    <t>agfERqgMzsU</t>
+  </si>
+  <si>
+    <t>Jfo92siBANg</t>
+  </si>
+  <si>
+    <t>iHodQZlsJHf</t>
+  </si>
+  <si>
+    <t>beBpDqUQJMn</t>
+  </si>
+  <si>
+    <t>I6Xcx9875kJ</t>
+  </si>
+  <si>
+    <t>xallQX8HUeS</t>
+  </si>
+  <si>
+    <t>S3jUrQJhdKZ</t>
+  </si>
+  <si>
+    <t>A1hzBiUAojv</t>
+  </si>
+  <si>
+    <t>Vli5C2SFWrh</t>
+  </si>
+  <si>
+    <t>BXOxuU6KIk2</t>
+  </si>
+  <si>
+    <t>PCPwwTlDOet</t>
+  </si>
+  <si>
+    <t>dtfYfdMxpyO</t>
+  </si>
+  <si>
+    <t>Cj3rwgMDm7q</t>
+  </si>
+  <si>
+    <t>sSb0uyx1KGX</t>
+  </si>
+  <si>
+    <t>qimGDSCAfDH</t>
+  </si>
+  <si>
+    <t>Qj5adNgRgcZ</t>
+  </si>
+  <si>
+    <t>ABHVdnREkwL</t>
+  </si>
+  <si>
+    <t>M2kNGRhQ8DW</t>
+  </si>
+  <si>
+    <t>rXXrT05BUkb</t>
+  </si>
+  <si>
+    <t>OB53vMjI2Qg</t>
+  </si>
+  <si>
+    <t>IgCp1lLEk3k</t>
+  </si>
+  <si>
+    <t>NeOAkzqDQr1</t>
+  </si>
+  <si>
+    <t>MUq9oPoC0hr</t>
+  </si>
+  <si>
+    <t>KeQO2qXn9TJ</t>
+  </si>
+  <si>
+    <t>ffgLF1M4YHa</t>
+  </si>
+  <si>
+    <t>yQcJZbzP2xr</t>
+  </si>
+  <si>
+    <t>vlE4I6quY2t</t>
+  </si>
+  <si>
+    <t>TKJOnOdCdI8</t>
+  </si>
+  <si>
+    <t>WH320Av0Uyf</t>
+  </si>
+  <si>
+    <t>OJd32TFeoRv</t>
+  </si>
+  <si>
+    <t>wVKbqMMIYuG</t>
+  </si>
+  <si>
+    <t>zkRGuZW2iEs</t>
+  </si>
+  <si>
+    <t>joIdF16QXGz</t>
+  </si>
+  <si>
+    <t>WZxMrmrEQ8w</t>
+  </si>
+  <si>
+    <t>IfzqFie8FFC</t>
+  </si>
+  <si>
+    <t>HZV6vjUIOuO</t>
+  </si>
+  <si>
+    <t>DKtToYhWt9D</t>
+  </si>
+  <si>
+    <t>QzzExnei6qC</t>
+  </si>
+  <si>
+    <t>QSHoDvRcExd</t>
+  </si>
+  <si>
+    <t>MBZ3v5JrcDo</t>
+  </si>
+  <si>
+    <t>AwNIudewIFl</t>
+  </si>
+  <si>
+    <t>SaEp4uCoKLh</t>
+  </si>
+  <si>
+    <t>q9iZUe3cVCu</t>
+  </si>
+  <si>
+    <t>AWDjfiWSCBU</t>
+  </si>
+  <si>
+    <t>RYgaEEnYq9o</t>
+  </si>
+  <si>
+    <t>raF128vcp7V</t>
+  </si>
+  <si>
+    <t>esRAsJYSOjw</t>
+  </si>
+  <si>
+    <t>KQy8LRpjAdS</t>
+  </si>
+  <si>
+    <t>TGJMCAUNXD5</t>
+  </si>
+  <si>
+    <t>lXcYHIFgbCM</t>
+  </si>
+  <si>
+    <t>miQ5RVnWC0K</t>
+  </si>
+  <si>
+    <t>XsnL6NMMrlI</t>
+  </si>
+  <si>
+    <t>OKPZ7SmaYwP</t>
+  </si>
+  <si>
+    <t>IEKVnEePZLN</t>
+  </si>
+  <si>
+    <t>lOzN4yw4pSh</t>
+  </si>
+  <si>
+    <t>zzy6njfXNHS</t>
+  </si>
+  <si>
+    <t>uYnfVI0bkyf</t>
+  </si>
+  <si>
+    <t>MySqArlwjyx</t>
+  </si>
+  <si>
+    <t>ABifpivVY4F</t>
+  </si>
+  <si>
+    <t>Jzpyxz1Cydy</t>
+  </si>
+  <si>
+    <t>YX4H2UI1YH1</t>
+  </si>
+  <si>
+    <t>pxYOOPUXmtt</t>
+  </si>
+  <si>
+    <t>rXi98mqvgVW</t>
+  </si>
+  <si>
+    <t>HMawTHcYFIg</t>
+  </si>
+  <si>
+    <t>mo0RQNCgRkz</t>
+  </si>
+  <si>
+    <t>iP3AXOcPWYS</t>
+  </si>
+  <si>
+    <t>rfjxOgpBAYp</t>
+  </si>
+  <si>
+    <t>sJDswuZ8Kqi</t>
+  </si>
+  <si>
+    <t>TUeKUGwfIua</t>
+  </si>
+  <si>
+    <t>iRAmuxfCqmA</t>
+  </si>
+  <si>
+    <t>QWFKuIQBs2o</t>
+  </si>
+  <si>
+    <t>TaFHmyxBqR7</t>
+  </si>
+  <si>
+    <t>ing1KSJHfV2</t>
+  </si>
+  <si>
+    <t>FfgZ5ufqf7n</t>
+  </si>
+  <si>
+    <t>Z58LnooMrl1</t>
+  </si>
+  <si>
+    <t>QEeLDER223e</t>
+  </si>
+  <si>
+    <t>p7CKerD8kRp</t>
+  </si>
+  <si>
+    <t>d6af619kvyy</t>
+  </si>
+  <si>
+    <t>gSmD81QO8FQ</t>
+  </si>
+  <si>
+    <t>HPvYjzYhInP</t>
+  </si>
+  <si>
+    <t>s4hetLU7YPE</t>
+  </si>
+  <si>
+    <t>DVOVgZ4doAK</t>
+  </si>
+  <si>
+    <t>S3gtlMZ4sYV</t>
+  </si>
+  <si>
+    <t>sjeTS3oSial</t>
+  </si>
+  <si>
+    <t>B5PbcJXLP9z</t>
+  </si>
+  <si>
+    <t>CLrRC2NZAR9</t>
+  </si>
+  <si>
+    <t>Oua590tZ4Vd</t>
+  </si>
+  <si>
+    <t>Sya1xqHhCCO</t>
+  </si>
+  <si>
+    <t>lJi4pRQnIsT</t>
+  </si>
+  <si>
+    <t>gpSSPDzNizj</t>
+  </si>
+  <si>
+    <t>bd3Do8Qlhvx</t>
+  </si>
+  <si>
+    <t>y4dTAIa0QOQ</t>
+  </si>
+  <si>
+    <t>MkLwSDRYf9F</t>
+  </si>
+  <si>
+    <t>uk9tTbaNcYv</t>
+  </si>
+  <si>
+    <t>vwiEyaxAxqF</t>
+  </si>
+  <si>
+    <t>lcNanbzK30q</t>
+  </si>
+  <si>
+    <t>NyZ328hbUiP</t>
+  </si>
+  <si>
+    <t>rGvzP3ihZ4b</t>
+  </si>
+  <si>
+    <t>lMUWyMQ19Nh</t>
+  </si>
+  <si>
+    <t>IA64rosyhK1</t>
+  </si>
+  <si>
+    <t>wdrwFa1Fa8F</t>
+  </si>
+  <si>
+    <t>yqwza0JgrOP</t>
+  </si>
+  <si>
+    <t>NIWuR5mfE9T</t>
+  </si>
+  <si>
+    <t>grDxsu9Yqk5</t>
+  </si>
+  <si>
+    <t>XgdchWPy1wD</t>
+  </si>
+  <si>
+    <t>q4KsTIBJvvk</t>
+  </si>
+  <si>
+    <t>SKTMJtbbsiU</t>
+  </si>
+  <si>
+    <t>fWFqufPpvlx</t>
+  </si>
+  <si>
+    <t>hkgcJhWm5cK</t>
+  </si>
+  <si>
+    <t>GupwPZYcMw1</t>
+  </si>
+  <si>
+    <t>fzYRxCwtQf2</t>
+  </si>
+  <si>
+    <t>wy6pj5TDsnM</t>
+  </si>
+  <si>
+    <t>CEs3GrO6OLy</t>
+  </si>
+  <si>
+    <t>J1dgQz1R68m</t>
+  </si>
+  <si>
+    <t>OdBvbhojEt7</t>
+  </si>
+  <si>
+    <t>uDnREpZJe2L</t>
+  </si>
+  <si>
+    <t>zghpaJrE7CP</t>
+  </si>
+  <si>
+    <t>OoBxXYn1eoy</t>
+  </si>
+  <si>
+    <t>dIgVADaXOoP</t>
+  </si>
+  <si>
+    <t>XndHVVSAz2n</t>
+  </si>
+  <si>
+    <t>t8NuQiiDWb6</t>
+  </si>
+  <si>
+    <t>akw2O5cpDNP</t>
+  </si>
+  <si>
+    <t>PBEQJpsapZw</t>
+  </si>
+  <si>
+    <t>gPw7wgxVzba</t>
+  </si>
+  <si>
+    <t>vjekFZFl4ee</t>
+  </si>
+  <si>
+    <t>rahBqbZYK7i</t>
+  </si>
+  <si>
+    <t>DouiDIYUwpD</t>
+  </si>
+  <si>
+    <t>wftHmLIxJmY</t>
+  </si>
+  <si>
+    <t>Lk5ycqeSJne</t>
+  </si>
+  <si>
+    <t>XVGyolmAns4</t>
+  </si>
+  <si>
+    <t>uYl0VNsBBfZ</t>
+  </si>
+  <si>
+    <t>Q1KhLwiGA2M</t>
+  </si>
+  <si>
+    <t>jq7EoZZx26g</t>
+  </si>
+  <si>
+    <t>cCOaMR3DYko</t>
+  </si>
+  <si>
+    <t>yjxtvOYtp5A</t>
+  </si>
+  <si>
+    <t>SvyAYrQ8Muc</t>
+  </si>
+  <si>
+    <t>AN9icOJ77De</t>
+  </si>
+  <si>
+    <t>io7CR9fOiUu</t>
+  </si>
+  <si>
+    <t>Df8G53YKehw</t>
+  </si>
+  <si>
+    <t>rYgatoDzAho</t>
+  </si>
+  <si>
+    <t>E22605q44Z6</t>
+  </si>
+  <si>
+    <t>ezo9FjVqXnX</t>
+  </si>
+  <si>
+    <t>NctJwmp66Nw</t>
+  </si>
+  <si>
+    <t>Ibj5WGv6mSf</t>
+  </si>
+  <si>
+    <t>xiBoESbWBRJ</t>
+  </si>
+  <si>
+    <t>xBnEEDeCGdx</t>
+  </si>
+  <si>
+    <t>Kzd0JboiGEE</t>
+  </si>
+  <si>
+    <t>TMlj3jekB4P</t>
+  </si>
+  <si>
+    <t>JRKjN1krw1v</t>
+  </si>
+  <si>
+    <t>LX58YZxVltq</t>
+  </si>
+  <si>
+    <t>vCsPrXuITbJ</t>
+  </si>
+  <si>
+    <t>bVDmQU3reY0</t>
+  </si>
+  <si>
+    <t>fiItxaKbEDp</t>
+  </si>
+  <si>
+    <t>UDc1iWITnyh</t>
+  </si>
+  <si>
+    <t>e2t30fu3vAw</t>
+  </si>
+  <si>
+    <t>eJfBtjef8cQ</t>
+  </si>
+  <si>
+    <t>zGZjhpdrOde</t>
+  </si>
+  <si>
+    <t>LJvUBIpAfxA</t>
+  </si>
+  <si>
+    <t>ENi2yTYsiwn</t>
+  </si>
+  <si>
+    <t>cLF5EECd41U</t>
+  </si>
+  <si>
+    <t>yox6XBHvvUs</t>
+  </si>
+  <si>
+    <t>wM3b4l8Oesq</t>
+  </si>
+  <si>
+    <t>qs0jtVhDtUn</t>
+  </si>
+  <si>
+    <t>iJYDbdwuZg8</t>
+  </si>
+  <si>
+    <t>msr1TOXqZKf</t>
+  </si>
+  <si>
+    <t>ZSSbDRTZ6CX</t>
+  </si>
+  <si>
+    <t>s4ZDSr4IBSr</t>
+  </si>
+  <si>
+    <t>dkIkLMCU3KL</t>
+  </si>
+  <si>
+    <t>P9qUQA6KmAs</t>
+  </si>
+  <si>
+    <t>agvc6ayfiXA</t>
+  </si>
+  <si>
+    <t>RkmYcI8HSzc</t>
+  </si>
+  <si>
+    <t>PRsuvBXN0uD</t>
+  </si>
+  <si>
+    <t>BoxL4OrNu9z</t>
+  </si>
+  <si>
+    <t>WgEYQP3iYOV</t>
+  </si>
+  <si>
+    <t>VQcbiMkzGaX</t>
+  </si>
+  <si>
+    <t>P9YGC19exdd</t>
+  </si>
+  <si>
+    <t>JiQnDPNGLSc</t>
+  </si>
+  <si>
+    <t>l1WeSm5Q2AH</t>
+  </si>
+  <si>
+    <t>zz3WHsntGAR</t>
+  </si>
+  <si>
+    <t>IX2qlVptNql</t>
+  </si>
+  <si>
+    <t>hsndZmGNruj</t>
+  </si>
+  <si>
+    <t>kDbYzGivY5E</t>
+  </si>
+  <si>
+    <t>SitHAvDM2cC</t>
+  </si>
+  <si>
+    <t>WbwyQeKEkqj</t>
+  </si>
+  <si>
+    <t>OADH3Y45nfz</t>
+  </si>
+  <si>
+    <t>ZKsPN6h4gio</t>
+  </si>
+  <si>
+    <t>zBZQENmVE6X</t>
+  </si>
+  <si>
+    <t>zc8MSk8QKes</t>
+  </si>
+  <si>
+    <t>SQNNLK6T2PE</t>
+  </si>
+  <si>
+    <t>FP21TAxHDmO</t>
+  </si>
+  <si>
+    <t>PwCPZwq4oB2</t>
+  </si>
+  <si>
+    <t>iO42gRTVa1j</t>
+  </si>
+  <si>
+    <t>OImQ8XTItmQ</t>
+  </si>
+  <si>
+    <t>qL1i6PdAYO1</t>
+  </si>
+  <si>
+    <t>ZDmz4A5zbfq</t>
+  </si>
+  <si>
+    <t>AqSY0XwLs09</t>
+  </si>
+  <si>
+    <t>loRPUW3Lkbh</t>
+  </si>
+  <si>
+    <t>V3MCCguBan8</t>
+  </si>
+  <si>
+    <t>NM4YEYMHEqN</t>
+  </si>
+  <si>
+    <t>tj7gQs8DwoM</t>
+  </si>
+  <si>
+    <t>IwQUgEBiiYB</t>
+  </si>
+  <si>
+    <t>H2vA8qHohf5</t>
+  </si>
+  <si>
+    <t>RkE3gsnXYGa</t>
+  </si>
+  <si>
+    <t>PeMBbhCoe0d</t>
+  </si>
+  <si>
+    <t>MUumX5cjk9g</t>
+  </si>
+  <si>
+    <t>ub62FSGJYq4</t>
+  </si>
+  <si>
+    <t>ixhlUJXZQl3</t>
+  </si>
+  <si>
+    <t>IrH54VuHKcN</t>
+  </si>
+  <si>
+    <t>QS61X8Xc1Tg</t>
+  </si>
+  <si>
+    <t>QqXS3kwHLkP</t>
+  </si>
+  <si>
+    <t>J3g5pfx4ImL</t>
+  </si>
+  <si>
+    <t>YDDAs3YqQlV</t>
+  </si>
+  <si>
+    <t>d6ugp5puEZ2</t>
+  </si>
+  <si>
+    <t>buoJs7KBYpv</t>
+  </si>
+  <si>
+    <t>MsWUEiTxyht</t>
+  </si>
+  <si>
+    <t>AOnYaVWWcMR</t>
+  </si>
+  <si>
+    <t>ySBhaLN97hO</t>
+  </si>
+  <si>
+    <t>w0fWsRSt3DY</t>
+  </si>
+  <si>
+    <t>k4Nw4uCT97V</t>
+  </si>
+  <si>
+    <t>U8JlS4N1LGd</t>
+  </si>
+  <si>
+    <t>hdJwrJJIVmt</t>
+  </si>
+  <si>
+    <t>dBES5aQviuh</t>
+  </si>
+  <si>
+    <t>xdRG6eDxhaR</t>
+  </si>
+  <si>
+    <t>ElMyEZ6ECq9</t>
+  </si>
+  <si>
+    <t>h3C9I5mdRrq</t>
+  </si>
+  <si>
+    <t>azIkyJZr7bZ</t>
+  </si>
+  <si>
+    <t>JnK78IWxALr</t>
+  </si>
+  <si>
+    <t>YDYCfFc8ndK</t>
+  </si>
+  <si>
+    <t>Cr1UF6ySgOc</t>
+  </si>
+  <si>
+    <t>JOocbzN2dq7</t>
+  </si>
+  <si>
+    <t>oZWwkGsF8WV</t>
+  </si>
+  <si>
+    <t>EQDiKgKYm0R</t>
+  </si>
+  <si>
+    <t>i3JqZR72D7n</t>
+  </si>
+  <si>
+    <t>wgIlO2aqNZX</t>
+  </si>
+  <si>
+    <t>hLbLWbrsyjK</t>
+  </si>
+  <si>
+    <t>aKMT7lcxjem</t>
+  </si>
+  <si>
+    <t>mQpnj5bT6HS</t>
+  </si>
+  <si>
+    <t>kdE66nb6IOn</t>
+  </si>
+  <si>
+    <t>fKjz5jJBSHU</t>
+  </si>
+  <si>
+    <t>pfM4t7cqVQl</t>
+  </si>
+  <si>
+    <t>AKfQkUjVHEK</t>
+  </si>
+  <si>
+    <t>TIy1pY845YA</t>
+  </si>
+  <si>
+    <t>R3wo354LTh8</t>
+  </si>
+  <si>
+    <t>PaWRhxkcNHc</t>
+  </si>
+  <si>
+    <t>oGnADi2isL3</t>
+  </si>
+  <si>
+    <t>ici8bVKMLTg</t>
+  </si>
+  <si>
+    <t>xNeqrHBHPb4</t>
+  </si>
+  <si>
+    <t>rAAA1eNbA72</t>
+  </si>
+  <si>
+    <t>VpbsAtJQcLk</t>
+  </si>
+  <si>
+    <t>C6f0etXoDZ2</t>
+  </si>
+  <si>
+    <t>NzwdCUPjLKM</t>
   </si>
 </sst>
 </file>
@@ -1601,15 +2702,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3A076C-ECA7-4854-BDDC-C813E3A40233}">
-  <dimension ref="A1:C374"/>
+  <dimension ref="A1:D372"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="66.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1619,8 +2721,11 @@
       <c r="C1" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1630,8 +2735,11 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1641,8 +2749,11 @@
       <c r="C3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1652,8 +2763,11 @@
       <c r="C4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1663,8 +2777,11 @@
       <c r="C5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -1674,8 +2791,11 @@
       <c r="C6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1685,8 +2805,11 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -1696,8 +2819,11 @@
       <c r="C8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -1707,8 +2833,11 @@
       <c r="C9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1718,8 +2847,11 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -1729,8 +2861,11 @@
       <c r="C11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -1740,8 +2875,11 @@
       <c r="C12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -1751,8 +2889,11 @@
       <c r="C13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -1762,8 +2903,11 @@
       <c r="C14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -1773,8 +2917,11 @@
       <c r="C15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1784,8 +2931,11 @@
       <c r="C16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1795,8 +2945,11 @@
       <c r="C17" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1806,8 +2959,11 @@
       <c r="C18" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1817,8 +2973,11 @@
       <c r="C19" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1828,8 +2987,11 @@
       <c r="C20" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -1839,8 +3001,11 @@
       <c r="C21" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -1850,8 +3015,11 @@
       <c r="C22" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -1861,8 +3029,11 @@
       <c r="C23" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -1872,8 +3043,11 @@
       <c r="C24" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -1883,8 +3057,11 @@
       <c r="C25" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -1894,8 +3071,11 @@
       <c r="C26" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -1905,8 +3085,11 @@
       <c r="C27" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -1916,8 +3099,11 @@
       <c r="C28" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -1927,8 +3113,11 @@
       <c r="C29" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -1938,8 +3127,11 @@
       <c r="C30" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -1949,8 +3141,11 @@
       <c r="C31" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -1960,8 +3155,11 @@
       <c r="C32" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -1971,8 +3169,11 @@
       <c r="C33" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -1982,8 +3183,11 @@
       <c r="C34" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -1993,8 +3197,11 @@
       <c r="C35" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -2004,8 +3211,11 @@
       <c r="C36" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -2015,8 +3225,11 @@
       <c r="C37" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -2026,8 +3239,11 @@
       <c r="C38" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -2037,8 +3253,11 @@
       <c r="C39" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -2048,8 +3267,11 @@
       <c r="C40" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -2059,8 +3281,11 @@
       <c r="C41" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -2070,8 +3295,11 @@
       <c r="C42" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -2081,8 +3309,11 @@
       <c r="C43" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -2092,8 +3323,11 @@
       <c r="C44" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -2103,8 +3337,11 @@
       <c r="C45" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -2114,8 +3351,11 @@
       <c r="C46" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -2125,8 +3365,11 @@
       <c r="C47" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -2136,10 +3379,13 @@
       <c r="C48" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B49" t="s">
         <v>53</v>
@@ -2147,19 +3393,25 @@
       <c r="C49" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="D50" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -2167,10 +3419,13 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="D51" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>17</v>
       </c>
@@ -2178,10 +3433,13 @@
         <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="D52" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>17</v>
       </c>
@@ -2189,10 +3447,13 @@
         <v>55</v>
       </c>
       <c r="C53" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="D53" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -2200,10 +3461,13 @@
         <v>55</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="D54" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -2211,10 +3475,13 @@
         <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="D55" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -2222,10 +3489,13 @@
         <v>55</v>
       </c>
       <c r="C56" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="D56" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -2233,10 +3503,13 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="D57" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -2244,10 +3517,13 @@
         <v>55</v>
       </c>
       <c r="C58" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="D58" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -2255,10 +3531,13 @@
         <v>55</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="D59" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -2266,10 +3545,13 @@
         <v>55</v>
       </c>
       <c r="C60" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="D60" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -2277,21 +3559,27 @@
         <v>55</v>
       </c>
       <c r="C61" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="D61" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="D62" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>2</v>
       </c>
@@ -2299,10 +3587,13 @@
         <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="D63" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>2</v>
       </c>
@@ -2310,10 +3601,13 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="D64" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -2321,10 +3615,13 @@
         <v>68</v>
       </c>
       <c r="C65" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="D65" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2332,10 +3629,13 @@
         <v>68</v>
       </c>
       <c r="C66" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="D66" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>2</v>
       </c>
@@ -2343,10 +3643,13 @@
         <v>68</v>
       </c>
       <c r="C67" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="D67" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>2</v>
       </c>
@@ -2354,10 +3657,13 @@
         <v>68</v>
       </c>
       <c r="C68" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D68" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>2</v>
       </c>
@@ -2365,10 +3671,13 @@
         <v>68</v>
       </c>
       <c r="C69" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="D69" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>2</v>
       </c>
@@ -2376,10 +3685,13 @@
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="D70" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>2</v>
       </c>
@@ -2387,10 +3699,13 @@
         <v>68</v>
       </c>
       <c r="C71" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="D71" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>2</v>
       </c>
@@ -2398,10 +3713,13 @@
         <v>68</v>
       </c>
       <c r="C72" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="D72" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>2</v>
       </c>
@@ -2409,10 +3727,13 @@
         <v>68</v>
       </c>
       <c r="C73" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="D73" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>2</v>
       </c>
@@ -2420,10 +3741,13 @@
         <v>68</v>
       </c>
       <c r="C74" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="D74" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>2</v>
       </c>
@@ -2431,10 +3755,13 @@
         <v>68</v>
       </c>
       <c r="C75" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="D75" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>2</v>
       </c>
@@ -2442,10 +3769,13 @@
         <v>68</v>
       </c>
       <c r="C76" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="D76" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>2</v>
       </c>
@@ -2453,10 +3783,13 @@
         <v>68</v>
       </c>
       <c r="C77" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="D77" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>2</v>
       </c>
@@ -2464,21 +3797,27 @@
         <v>68</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="D78" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="B79" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C79" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="D79" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>52</v>
       </c>
@@ -2486,10 +3825,13 @@
         <v>86</v>
       </c>
       <c r="C80" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="D80" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>52</v>
       </c>
@@ -2497,10 +3839,13 @@
         <v>86</v>
       </c>
       <c r="C81" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="D81" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>52</v>
       </c>
@@ -2508,10 +3853,13 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="D82" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>52</v>
       </c>
@@ -2519,10 +3867,13 @@
         <v>86</v>
       </c>
       <c r="C83" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="D83" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>52</v>
       </c>
@@ -2530,10 +3881,13 @@
         <v>86</v>
       </c>
       <c r="C84" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="D84" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>52</v>
       </c>
@@ -2541,10 +3895,13 @@
         <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="D85" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>52</v>
       </c>
@@ -2552,10 +3909,13 @@
         <v>86</v>
       </c>
       <c r="C86" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="D86" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>52</v>
       </c>
@@ -2563,10 +3923,13 @@
         <v>86</v>
       </c>
       <c r="C87" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="D87" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>52</v>
       </c>
@@ -2574,10 +3937,13 @@
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="D88" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>52</v>
       </c>
@@ -2585,10 +3951,13 @@
         <v>86</v>
       </c>
       <c r="C89" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="D89" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>52</v>
       </c>
@@ -2596,10 +3965,13 @@
         <v>86</v>
       </c>
       <c r="C90" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="D90" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>52</v>
       </c>
@@ -2607,10 +3979,13 @@
         <v>86</v>
       </c>
       <c r="C91" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="D91" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>52</v>
       </c>
@@ -2618,10 +3993,13 @@
         <v>86</v>
       </c>
       <c r="C92" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="D92" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>52</v>
       </c>
@@ -2629,10 +4007,13 @@
         <v>86</v>
       </c>
       <c r="C93" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="D93" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>52</v>
       </c>
@@ -2640,10 +4021,13 @@
         <v>86</v>
       </c>
       <c r="C94" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="D94" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>52</v>
       </c>
@@ -2651,21 +4035,27 @@
         <v>86</v>
       </c>
       <c r="C95" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="D95" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>52</v>
       </c>
       <c r="B96" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C96" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="D96" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>52</v>
       </c>
@@ -2673,10 +4063,13 @@
         <v>104</v>
       </c>
       <c r="C97" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="D97" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>52</v>
       </c>
@@ -2684,10 +4077,13 @@
         <v>104</v>
       </c>
       <c r="C98" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="D98" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>52</v>
       </c>
@@ -2695,10 +4091,13 @@
         <v>104</v>
       </c>
       <c r="C99" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="D99" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>52</v>
       </c>
@@ -2706,10 +4105,13 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="D100" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>52</v>
       </c>
@@ -2717,10 +4119,13 @@
         <v>104</v>
       </c>
       <c r="C101" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="D101" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>52</v>
       </c>
@@ -2728,10 +4133,13 @@
         <v>104</v>
       </c>
       <c r="C102" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="D102" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>52</v>
       </c>
@@ -2739,10 +4147,13 @@
         <v>104</v>
       </c>
       <c r="C103" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="D103" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>52</v>
       </c>
@@ -2750,10 +4161,13 @@
         <v>104</v>
       </c>
       <c r="C104" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="D104" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>52</v>
       </c>
@@ -2761,10 +4175,13 @@
         <v>104</v>
       </c>
       <c r="C105" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="D105" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>52</v>
       </c>
@@ -2772,10 +4189,13 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="D106" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>52</v>
       </c>
@@ -2783,10 +4203,13 @@
         <v>104</v>
       </c>
       <c r="C107" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="D107" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>52</v>
       </c>
@@ -2794,10 +4217,13 @@
         <v>104</v>
       </c>
       <c r="C108" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="D108" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>52</v>
       </c>
@@ -2805,10 +4231,13 @@
         <v>104</v>
       </c>
       <c r="C109" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="D109" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>52</v>
       </c>
@@ -2816,10 +4245,13 @@
         <v>104</v>
       </c>
       <c r="C110" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="D110" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>52</v>
       </c>
@@ -2827,10 +4259,13 @@
         <v>104</v>
       </c>
       <c r="C111" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="D111" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>52</v>
       </c>
@@ -2838,10 +4273,13 @@
         <v>104</v>
       </c>
       <c r="C112" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="D112" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>52</v>
       </c>
@@ -2849,10 +4287,13 @@
         <v>104</v>
       </c>
       <c r="C113" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+      <c r="D113" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>52</v>
       </c>
@@ -2860,10 +4301,13 @@
         <v>104</v>
       </c>
       <c r="C114" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="D114" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>52</v>
       </c>
@@ -2871,10 +4315,13 @@
         <v>104</v>
       </c>
       <c r="C115" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="D115" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>52</v>
       </c>
@@ -2882,10 +4329,13 @@
         <v>104</v>
       </c>
       <c r="C116" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+      <c r="D116" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>52</v>
       </c>
@@ -2893,10 +4343,13 @@
         <v>104</v>
       </c>
       <c r="C117" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="D117" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>52</v>
       </c>
@@ -2904,10 +4357,13 @@
         <v>104</v>
       </c>
       <c r="C118" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="D118" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>52</v>
       </c>
@@ -2915,10 +4371,13 @@
         <v>104</v>
       </c>
       <c r="C119" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="D119" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>52</v>
       </c>
@@ -2926,10 +4385,13 @@
         <v>104</v>
       </c>
       <c r="C120" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+      <c r="D120" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>52</v>
       </c>
@@ -2937,10 +4399,13 @@
         <v>104</v>
       </c>
       <c r="C121" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="D121" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>52</v>
       </c>
@@ -2948,10 +4413,13 @@
         <v>104</v>
       </c>
       <c r="C122" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="D122" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>52</v>
       </c>
@@ -2959,10 +4427,13 @@
         <v>104</v>
       </c>
       <c r="C123" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="D123" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>52</v>
       </c>
@@ -2970,10 +4441,13 @@
         <v>104</v>
       </c>
       <c r="C124" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="D124" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>52</v>
       </c>
@@ -2981,10 +4455,13 @@
         <v>104</v>
       </c>
       <c r="C125" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="D125" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>52</v>
       </c>
@@ -2992,21 +4469,27 @@
         <v>104</v>
       </c>
       <c r="C126" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="D126" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="B127" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C127" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="D127" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>17</v>
       </c>
@@ -3014,10 +4497,13 @@
         <v>136</v>
       </c>
       <c r="C128" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="D128" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>17</v>
       </c>
@@ -3025,10 +4511,13 @@
         <v>136</v>
       </c>
       <c r="C129" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="D129" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>17</v>
       </c>
@@ -3036,10 +4525,10 @@
         <v>136</v>
       </c>
       <c r="C130" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>17</v>
       </c>
@@ -3047,10 +4536,13 @@
         <v>136</v>
       </c>
       <c r="C131" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="D131" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>17</v>
       </c>
@@ -3058,10 +4550,13 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="D132" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>17</v>
       </c>
@@ -3069,10 +4564,13 @@
         <v>136</v>
       </c>
       <c r="C133" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="D133" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>17</v>
       </c>
@@ -3080,10 +4578,13 @@
         <v>136</v>
       </c>
       <c r="C134" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+      <c r="D134" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>17</v>
       </c>
@@ -3091,10 +4592,13 @@
         <v>136</v>
       </c>
       <c r="C135" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+      <c r="D135" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>17</v>
       </c>
@@ -3102,10 +4606,13 @@
         <v>136</v>
       </c>
       <c r="C136" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+      <c r="D136" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>17</v>
       </c>
@@ -3113,10 +4620,13 @@
         <v>136</v>
       </c>
       <c r="C137" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+      <c r="D137" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>17</v>
       </c>
@@ -3124,10 +4634,13 @@
         <v>136</v>
       </c>
       <c r="C138" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+      <c r="D138" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>17</v>
       </c>
@@ -3135,10 +4648,13 @@
         <v>136</v>
       </c>
       <c r="C139" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="D139" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>17</v>
       </c>
@@ -3146,21 +4662,27 @@
         <v>136</v>
       </c>
       <c r="C140" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="D140" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="B141" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="C141" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="D141" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>52</v>
       </c>
@@ -3168,10 +4690,13 @@
         <v>151</v>
       </c>
       <c r="C142" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="D142" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>52</v>
       </c>
@@ -3179,10 +4704,13 @@
         <v>151</v>
       </c>
       <c r="C143" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="D143" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>52</v>
       </c>
@@ -3190,10 +4718,13 @@
         <v>151</v>
       </c>
       <c r="C144" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="D144" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>52</v>
       </c>
@@ -3201,10 +4732,13 @@
         <v>151</v>
       </c>
       <c r="C145" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="D145" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>52</v>
       </c>
@@ -3212,10 +4746,13 @@
         <v>151</v>
       </c>
       <c r="C146" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="D146" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>52</v>
       </c>
@@ -3223,10 +4760,13 @@
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="D147" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>52</v>
       </c>
@@ -3234,10 +4774,13 @@
         <v>151</v>
       </c>
       <c r="C148" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+      <c r="D148" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>52</v>
       </c>
@@ -3245,10 +4788,13 @@
         <v>151</v>
       </c>
       <c r="C149" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="D149" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>52</v>
       </c>
@@ -3256,10 +4802,13 @@
         <v>151</v>
       </c>
       <c r="C150" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="D150" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>52</v>
       </c>
@@ -3267,10 +4816,13 @@
         <v>151</v>
       </c>
       <c r="C151" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="D151" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>52</v>
       </c>
@@ -3278,10 +4830,13 @@
         <v>151</v>
       </c>
       <c r="C152" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="D152" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>52</v>
       </c>
@@ -3289,10 +4844,13 @@
         <v>151</v>
       </c>
       <c r="C153" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="D153" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>52</v>
       </c>
@@ -3300,21 +4858,27 @@
         <v>151</v>
       </c>
       <c r="C154" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="D154" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>52</v>
+        <v>166</v>
       </c>
       <c r="B155" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C155" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="D155" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>166</v>
       </c>
@@ -3322,10 +4886,13 @@
         <v>167</v>
       </c>
       <c r="C156" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="D156" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>166</v>
       </c>
@@ -3333,10 +4900,13 @@
         <v>167</v>
       </c>
       <c r="C157" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="D157" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>166</v>
       </c>
@@ -3344,10 +4914,13 @@
         <v>167</v>
       </c>
       <c r="C158" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="D158" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>166</v>
       </c>
@@ -3355,10 +4928,13 @@
         <v>167</v>
       </c>
       <c r="C159" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+      <c r="D159" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>166</v>
       </c>
@@ -3366,10 +4942,13 @@
         <v>167</v>
       </c>
       <c r="C160" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="D160" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>166</v>
       </c>
@@ -3377,10 +4956,13 @@
         <v>167</v>
       </c>
       <c r="C161" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+      <c r="D161" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>166</v>
       </c>
@@ -3388,10 +4970,13 @@
         <v>167</v>
       </c>
       <c r="C162" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="D162" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>166</v>
       </c>
@@ -3399,10 +4984,13 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+      <c r="D163" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>166</v>
       </c>
@@ -3410,10 +4998,13 @@
         <v>167</v>
       </c>
       <c r="C164" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="D164" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>166</v>
       </c>
@@ -3421,10 +5012,13 @@
         <v>167</v>
       </c>
       <c r="C165" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="D165" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>166</v>
       </c>
@@ -3432,10 +5026,13 @@
         <v>167</v>
       </c>
       <c r="C166" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+      <c r="D166" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>166</v>
       </c>
@@ -3443,10 +5040,13 @@
         <v>167</v>
       </c>
       <c r="C167" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="D167" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>166</v>
       </c>
@@ -3454,10 +5054,13 @@
         <v>167</v>
       </c>
       <c r="C168" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="D168" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>166</v>
       </c>
@@ -3465,10 +5068,13 @@
         <v>167</v>
       </c>
       <c r="C169" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="D169" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>166</v>
       </c>
@@ -3476,10 +5082,13 @@
         <v>167</v>
       </c>
       <c r="C170" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="D170" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>166</v>
       </c>
@@ -3487,10 +5096,13 @@
         <v>167</v>
       </c>
       <c r="C171" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="D171" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>166</v>
       </c>
@@ -3498,10 +5110,13 @@
         <v>167</v>
       </c>
       <c r="C172" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+      <c r="D172" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>166</v>
       </c>
@@ -3509,10 +5124,13 @@
         <v>167</v>
       </c>
       <c r="C173" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+      <c r="D173" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>166</v>
       </c>
@@ -3520,21 +5138,27 @@
         <v>167</v>
       </c>
       <c r="C174" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="D174" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="B175" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C175" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D175" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>188</v>
       </c>
@@ -3542,10 +5166,13 @@
         <v>189</v>
       </c>
       <c r="C176" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+      <c r="D176" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>188</v>
       </c>
@@ -3553,10 +5180,13 @@
         <v>189</v>
       </c>
       <c r="C177" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+      <c r="D177" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>188</v>
       </c>
@@ -3564,10 +5194,13 @@
         <v>189</v>
       </c>
       <c r="C178" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="D178" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>188</v>
       </c>
@@ -3575,10 +5208,13 @@
         <v>189</v>
       </c>
       <c r="C179" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+      <c r="D179" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>188</v>
       </c>
@@ -3586,10 +5222,13 @@
         <v>189</v>
       </c>
       <c r="C180" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+      <c r="D180" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>188</v>
       </c>
@@ -3597,10 +5236,13 @@
         <v>189</v>
       </c>
       <c r="C181" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+      <c r="D181" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>188</v>
       </c>
@@ -3608,10 +5250,13 @@
         <v>189</v>
       </c>
       <c r="C182" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+      <c r="D182" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>188</v>
       </c>
@@ -3619,10 +5264,13 @@
         <v>189</v>
       </c>
       <c r="C183" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="D183" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>188</v>
       </c>
@@ -3630,10 +5278,13 @@
         <v>189</v>
       </c>
       <c r="C184" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+      <c r="D184" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>188</v>
       </c>
@@ -3641,10 +5292,13 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="D185" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>188</v>
       </c>
@@ -3652,10 +5306,13 @@
         <v>189</v>
       </c>
       <c r="C186" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+      <c r="D186" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>188</v>
       </c>
@@ -3663,10 +5320,13 @@
         <v>189</v>
       </c>
       <c r="C187" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="D187" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>188</v>
       </c>
@@ -3674,10 +5334,13 @@
         <v>189</v>
       </c>
       <c r="C188" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+      <c r="D188" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>188</v>
       </c>
@@ -3685,10 +5348,13 @@
         <v>189</v>
       </c>
       <c r="C189" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+      <c r="D189" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>188</v>
       </c>
@@ -3696,10 +5362,13 @@
         <v>189</v>
       </c>
       <c r="C190" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+      <c r="D190" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>188</v>
       </c>
@@ -3707,10 +5376,13 @@
         <v>189</v>
       </c>
       <c r="C191" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+      <c r="D191" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>188</v>
       </c>
@@ -3718,10 +5390,13 @@
         <v>189</v>
       </c>
       <c r="C192" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="D192" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>188</v>
       </c>
@@ -3729,10 +5404,13 @@
         <v>189</v>
       </c>
       <c r="C193" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+      <c r="D193" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>188</v>
       </c>
@@ -3740,10 +5418,13 @@
         <v>189</v>
       </c>
       <c r="C194" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+      <c r="D194" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>188</v>
       </c>
@@ -3751,10 +5432,13 @@
         <v>189</v>
       </c>
       <c r="C195" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="D195" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>188</v>
       </c>
@@ -3762,21 +5446,27 @@
         <v>189</v>
       </c>
       <c r="C196" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+      <c r="D196" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>188</v>
       </c>
       <c r="B197" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C197" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="D197" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>188</v>
       </c>
@@ -3784,10 +5474,13 @@
         <v>211</v>
       </c>
       <c r="C198" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="D198" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>188</v>
       </c>
@@ -3795,10 +5488,13 @@
         <v>211</v>
       </c>
       <c r="C199" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="D199" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>188</v>
       </c>
@@ -3806,10 +5502,13 @@
         <v>211</v>
       </c>
       <c r="C200" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="D200" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>188</v>
       </c>
@@ -3817,10 +5516,13 @@
         <v>211</v>
       </c>
       <c r="C201" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+      <c r="D201" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>188</v>
       </c>
@@ -3828,10 +5530,13 @@
         <v>211</v>
       </c>
       <c r="C202" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+      <c r="D202" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>188</v>
       </c>
@@ -3839,10 +5544,13 @@
         <v>211</v>
       </c>
       <c r="C203" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="D203" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>188</v>
       </c>
@@ -3850,10 +5558,13 @@
         <v>211</v>
       </c>
       <c r="C204" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+      <c r="D204" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>188</v>
       </c>
@@ -3861,10 +5572,13 @@
         <v>211</v>
       </c>
       <c r="C205" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="D205" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>188</v>
       </c>
@@ -3872,10 +5586,13 @@
         <v>211</v>
       </c>
       <c r="C206" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+      <c r="D206" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>188</v>
       </c>
@@ -3883,10 +5600,13 @@
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="D207" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>188</v>
       </c>
@@ -3894,10 +5614,13 @@
         <v>211</v>
       </c>
       <c r="C208" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="D208" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>188</v>
       </c>
@@ -3905,10 +5628,13 @@
         <v>211</v>
       </c>
       <c r="C209" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+      <c r="D209" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>188</v>
       </c>
@@ -3916,21 +5642,27 @@
         <v>211</v>
       </c>
       <c r="C210" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+      <c r="D210" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="C211" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+      <c r="D211" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>166</v>
       </c>
@@ -3938,10 +5670,13 @@
         <v>226</v>
       </c>
       <c r="C212" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+      <c r="D212" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>166</v>
       </c>
@@ -3949,10 +5684,13 @@
         <v>226</v>
       </c>
       <c r="C213" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+      <c r="D213" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>166</v>
       </c>
@@ -3960,10 +5698,13 @@
         <v>226</v>
       </c>
       <c r="C214" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+      <c r="D214" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>166</v>
       </c>
@@ -3971,10 +5712,13 @@
         <v>226</v>
       </c>
       <c r="C215" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+      <c r="D215" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>166</v>
       </c>
@@ -3982,10 +5726,13 @@
         <v>226</v>
       </c>
       <c r="C216" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="D216" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>166</v>
       </c>
@@ -3993,10 +5740,13 @@
         <v>226</v>
       </c>
       <c r="C217" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+      <c r="D217" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>166</v>
       </c>
@@ -4004,10 +5754,13 @@
         <v>226</v>
       </c>
       <c r="C218" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+      <c r="D218" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>166</v>
       </c>
@@ -4015,10 +5768,13 @@
         <v>226</v>
       </c>
       <c r="C219" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+      <c r="D219" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>166</v>
       </c>
@@ -4026,10 +5782,13 @@
         <v>226</v>
       </c>
       <c r="C220" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="D220" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>166</v>
       </c>
@@ -4037,21 +5796,27 @@
         <v>226</v>
       </c>
       <c r="C221" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="D221" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>166</v>
+        <v>52</v>
       </c>
       <c r="B222" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="C222" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="D222" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>52</v>
       </c>
@@ -4059,10 +5824,13 @@
         <v>238</v>
       </c>
       <c r="C223" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+      <c r="D223" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>52</v>
       </c>
@@ -4070,10 +5838,13 @@
         <v>238</v>
       </c>
       <c r="C224" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+      <c r="D224" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>52</v>
       </c>
@@ -4081,10 +5852,13 @@
         <v>238</v>
       </c>
       <c r="C225" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+      <c r="D225" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>52</v>
       </c>
@@ -4092,10 +5866,13 @@
         <v>238</v>
       </c>
       <c r="C226" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+      <c r="D226" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>52</v>
       </c>
@@ -4103,10 +5880,13 @@
         <v>238</v>
       </c>
       <c r="C227" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="D227" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>52</v>
       </c>
@@ -4114,10 +5894,13 @@
         <v>238</v>
       </c>
       <c r="C228" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+      <c r="D228" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>52</v>
       </c>
@@ -4125,10 +5908,13 @@
         <v>238</v>
       </c>
       <c r="C229" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+      <c r="D229" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>52</v>
       </c>
@@ -4136,10 +5922,13 @@
         <v>238</v>
       </c>
       <c r="C230" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+      <c r="D230" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>52</v>
       </c>
@@ -4147,10 +5936,13 @@
         <v>238</v>
       </c>
       <c r="C231" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+      <c r="D231" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>52</v>
       </c>
@@ -4158,10 +5950,13 @@
         <v>238</v>
       </c>
       <c r="C232" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+      <c r="D232" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>52</v>
       </c>
@@ -4169,10 +5964,13 @@
         <v>238</v>
       </c>
       <c r="C233" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+      <c r="D233" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>52</v>
       </c>
@@ -4180,10 +5978,13 @@
         <v>238</v>
       </c>
       <c r="C234" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+      <c r="D234" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>52</v>
       </c>
@@ -4191,10 +5992,13 @@
         <v>238</v>
       </c>
       <c r="C235" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+      <c r="D235" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>52</v>
       </c>
@@ -4202,21 +6006,27 @@
         <v>238</v>
       </c>
       <c r="C236" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="D236" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>52</v>
+        <v>166</v>
       </c>
       <c r="B237" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="C237" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="D237" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>166</v>
       </c>
@@ -4224,10 +6034,13 @@
         <v>254</v>
       </c>
       <c r="C238" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+      <c r="D238" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>166</v>
       </c>
@@ -4235,10 +6048,13 @@
         <v>254</v>
       </c>
       <c r="C239" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="D239" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>166</v>
       </c>
@@ -4246,10 +6062,13 @@
         <v>254</v>
       </c>
       <c r="C240" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+      <c r="D240" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>166</v>
       </c>
@@ -4257,10 +6076,13 @@
         <v>254</v>
       </c>
       <c r="C241" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="D241" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>166</v>
       </c>
@@ -4268,10 +6090,13 @@
         <v>254</v>
       </c>
       <c r="C242" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+      <c r="D242" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>166</v>
       </c>
@@ -4279,10 +6104,13 @@
         <v>254</v>
       </c>
       <c r="C243" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="D243" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>166</v>
       </c>
@@ -4290,10 +6118,13 @@
         <v>254</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+      <c r="D244" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>166</v>
       </c>
@@ -4301,10 +6132,13 @@
         <v>254</v>
       </c>
       <c r="C245" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+      <c r="D245" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>166</v>
       </c>
@@ -4312,10 +6146,13 @@
         <v>254</v>
       </c>
       <c r="C246" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+      <c r="D246" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>166</v>
       </c>
@@ -4323,10 +6160,13 @@
         <v>254</v>
       </c>
       <c r="C247" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+      <c r="D247" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>166</v>
       </c>
@@ -4334,10 +6174,13 @@
         <v>254</v>
       </c>
       <c r="C248" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+      <c r="D248" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>166</v>
       </c>
@@ -4345,10 +6188,13 @@
         <v>254</v>
       </c>
       <c r="C249" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="D249" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>166</v>
       </c>
@@ -4356,10 +6202,13 @@
         <v>254</v>
       </c>
       <c r="C250" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+      <c r="D250" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>166</v>
       </c>
@@ -4367,10 +6216,13 @@
         <v>254</v>
       </c>
       <c r="C251" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+      <c r="D251" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>166</v>
       </c>
@@ -4378,10 +6230,13 @@
         <v>254</v>
       </c>
       <c r="C252" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="D252" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>166</v>
       </c>
@@ -4389,10 +6244,13 @@
         <v>254</v>
       </c>
       <c r="C253" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+      <c r="D253" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>166</v>
       </c>
@@ -4400,10 +6258,13 @@
         <v>254</v>
       </c>
       <c r="C254" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+      <c r="D254" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>166</v>
       </c>
@@ -4411,10 +6272,13 @@
         <v>254</v>
       </c>
       <c r="C255" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="D255" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>166</v>
       </c>
@@ -4422,21 +6286,27 @@
         <v>254</v>
       </c>
       <c r="C256" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+      <c r="D256" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>166</v>
       </c>
       <c r="B257" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="C257" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+      <c r="D257" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>166</v>
       </c>
@@ -4444,10 +6314,13 @@
         <v>275</v>
       </c>
       <c r="C258" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+      <c r="D258" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>166</v>
       </c>
@@ -4455,10 +6328,13 @@
         <v>275</v>
       </c>
       <c r="C259" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+      <c r="D259" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>166</v>
       </c>
@@ -4466,10 +6342,13 @@
         <v>275</v>
       </c>
       <c r="C260" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+      <c r="D260" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>166</v>
       </c>
@@ -4477,10 +6356,13 @@
         <v>275</v>
       </c>
       <c r="C261" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+      <c r="D261" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>166</v>
       </c>
@@ -4488,10 +6370,13 @@
         <v>275</v>
       </c>
       <c r="C262" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+      <c r="D262" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>166</v>
       </c>
@@ -4499,10 +6384,13 @@
         <v>275</v>
       </c>
       <c r="C263" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+      <c r="D263" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>166</v>
       </c>
@@ -4510,10 +6398,13 @@
         <v>275</v>
       </c>
       <c r="C264" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+      <c r="D264" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>166</v>
       </c>
@@ -4521,10 +6412,13 @@
         <v>275</v>
       </c>
       <c r="C265" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+      <c r="D265" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>166</v>
       </c>
@@ -4532,10 +6426,13 @@
         <v>275</v>
       </c>
       <c r="C266" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+      <c r="D266" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>166</v>
       </c>
@@ -4543,10 +6440,13 @@
         <v>275</v>
       </c>
       <c r="C267" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+      <c r="D267" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>166</v>
       </c>
@@ -4554,10 +6454,13 @@
         <v>275</v>
       </c>
       <c r="C268" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+      <c r="D268" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>166</v>
       </c>
@@ -4565,21 +6468,27 @@
         <v>275</v>
       </c>
       <c r="C269" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+      <c r="D269" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="B270" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="C270" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+      <c r="D270" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>188</v>
       </c>
@@ -4587,10 +6496,13 @@
         <v>288</v>
       </c>
       <c r="C271" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+      <c r="D271" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>188</v>
       </c>
@@ -4598,10 +6510,13 @@
         <v>288</v>
       </c>
       <c r="C272" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+      <c r="D272" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>188</v>
       </c>
@@ -4609,10 +6524,13 @@
         <v>288</v>
       </c>
       <c r="C273" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+      <c r="D273" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>188</v>
       </c>
@@ -4620,10 +6538,13 @@
         <v>288</v>
       </c>
       <c r="C274" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+      <c r="D274" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>188</v>
       </c>
@@ -4631,10 +6552,13 @@
         <v>288</v>
       </c>
       <c r="C275" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+      <c r="D275" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>188</v>
       </c>
@@ -4642,10 +6566,13 @@
         <v>288</v>
       </c>
       <c r="C276" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+      <c r="D276" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>188</v>
       </c>
@@ -4653,10 +6580,13 @@
         <v>288</v>
       </c>
       <c r="C277" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+      <c r="D277" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>188</v>
       </c>
@@ -4664,10 +6594,13 @@
         <v>288</v>
       </c>
       <c r="C278" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+      <c r="D278" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>188</v>
       </c>
@@ -4675,10 +6608,13 @@
         <v>288</v>
       </c>
       <c r="C279" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="D279" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>188</v>
       </c>
@@ -4686,10 +6622,13 @@
         <v>288</v>
       </c>
       <c r="C280" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+      <c r="D280" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>188</v>
       </c>
@@ -4697,10 +6636,13 @@
         <v>288</v>
       </c>
       <c r="C281" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="D281" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>188</v>
       </c>
@@ -4708,10 +6650,13 @@
         <v>288</v>
       </c>
       <c r="C282" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="D282" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>188</v>
       </c>
@@ -4719,10 +6664,13 @@
         <v>288</v>
       </c>
       <c r="C283" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+      <c r="D283" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>188</v>
       </c>
@@ -4730,10 +6678,13 @@
         <v>288</v>
       </c>
       <c r="C284" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+      <c r="D284" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>188</v>
       </c>
@@ -4741,10 +6692,13 @@
         <v>288</v>
       </c>
       <c r="C285" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+      <c r="D285" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>188</v>
       </c>
@@ -4752,21 +6706,27 @@
         <v>288</v>
       </c>
       <c r="C286" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+      <c r="D286" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>188</v>
       </c>
       <c r="B287" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C287" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+      <c r="D287" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>188</v>
       </c>
@@ -4774,10 +6734,13 @@
         <v>306</v>
       </c>
       <c r="C288" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+      <c r="D288" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>188</v>
       </c>
@@ -4785,10 +6748,13 @@
         <v>306</v>
       </c>
       <c r="C289" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+      <c r="D289" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>188</v>
       </c>
@@ -4796,10 +6762,13 @@
         <v>306</v>
       </c>
       <c r="C290" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+      <c r="D290" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>188</v>
       </c>
@@ -4807,10 +6776,13 @@
         <v>306</v>
       </c>
       <c r="C291" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+      <c r="D291" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>188</v>
       </c>
@@ -4818,10 +6790,13 @@
         <v>306</v>
       </c>
       <c r="C292" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+      <c r="D292" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>188</v>
       </c>
@@ -4829,10 +6804,13 @@
         <v>306</v>
       </c>
       <c r="C293" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+      <c r="D293" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>188</v>
       </c>
@@ -4840,10 +6818,13 @@
         <v>306</v>
       </c>
       <c r="C294" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+      <c r="D294" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>188</v>
       </c>
@@ -4851,10 +6832,13 @@
         <v>306</v>
       </c>
       <c r="C295" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+      <c r="D295" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>188</v>
       </c>
@@ -4862,10 +6846,13 @@
         <v>306</v>
       </c>
       <c r="C296" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+      <c r="D296" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>188</v>
       </c>
@@ -4873,10 +6860,13 @@
         <v>306</v>
       </c>
       <c r="C297" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+      <c r="D297" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>188</v>
       </c>
@@ -4884,10 +6874,13 @@
         <v>306</v>
       </c>
       <c r="C298" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+      <c r="D298" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>188</v>
       </c>
@@ -4895,10 +6888,13 @@
         <v>306</v>
       </c>
       <c r="C299" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+      <c r="D299" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>188</v>
       </c>
@@ -4906,10 +6902,13 @@
         <v>306</v>
       </c>
       <c r="C300" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+      <c r="D300" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>188</v>
       </c>
@@ -4917,10 +6916,13 @@
         <v>306</v>
       </c>
       <c r="C301" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+      <c r="D301" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>188</v>
       </c>
@@ -4928,10 +6930,13 @@
         <v>306</v>
       </c>
       <c r="C302" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+      <c r="D302" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>188</v>
       </c>
@@ -4939,10 +6944,13 @@
         <v>306</v>
       </c>
       <c r="C303" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="D303" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>188</v>
       </c>
@@ -4950,10 +6958,13 @@
         <v>306</v>
       </c>
       <c r="C304" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+      <c r="D304" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>188</v>
       </c>
@@ -4961,10 +6972,13 @@
         <v>306</v>
       </c>
       <c r="C305" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+      <c r="D305" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>188</v>
       </c>
@@ -4972,21 +6986,27 @@
         <v>306</v>
       </c>
       <c r="C306" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+      <c r="D306" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>188</v>
       </c>
       <c r="B307" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="C307" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+      <c r="D307" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>188</v>
       </c>
@@ -4994,10 +7014,13 @@
         <v>327</v>
       </c>
       <c r="C308" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="D308" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>188</v>
       </c>
@@ -5005,10 +7028,13 @@
         <v>327</v>
       </c>
       <c r="C309" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+      <c r="D309" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>188</v>
       </c>
@@ -5016,10 +7042,13 @@
         <v>327</v>
       </c>
       <c r="C310" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+      <c r="D310" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>188</v>
       </c>
@@ -5027,10 +7056,13 @@
         <v>327</v>
       </c>
       <c r="C311" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+      <c r="D311" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>188</v>
       </c>
@@ -5038,10 +7070,13 @@
         <v>327</v>
       </c>
       <c r="C312" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+        <v>333</v>
+      </c>
+      <c r="D312" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>188</v>
       </c>
@@ -5049,10 +7084,13 @@
         <v>327</v>
       </c>
       <c r="C313" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+      <c r="D313" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>188</v>
       </c>
@@ -5060,10 +7098,13 @@
         <v>327</v>
       </c>
       <c r="C314" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+      <c r="D314" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>188</v>
       </c>
@@ -5071,10 +7112,13 @@
         <v>327</v>
       </c>
       <c r="C315" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+      <c r="D315" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>188</v>
       </c>
@@ -5082,10 +7126,13 @@
         <v>327</v>
       </c>
       <c r="C316" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+      <c r="D316" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>188</v>
       </c>
@@ -5093,10 +7140,13 @@
         <v>327</v>
       </c>
       <c r="C317" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+      <c r="D317" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>188</v>
       </c>
@@ -5104,10 +7154,13 @@
         <v>327</v>
       </c>
       <c r="C318" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="D318" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>188</v>
       </c>
@@ -5115,10 +7168,13 @@
         <v>327</v>
       </c>
       <c r="C319" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+      <c r="D319" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>188</v>
       </c>
@@ -5126,10 +7182,13 @@
         <v>327</v>
       </c>
       <c r="C320" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+      <c r="D320" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>188</v>
       </c>
@@ -5137,10 +7196,13 @@
         <v>327</v>
       </c>
       <c r="C321" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+        <v>342</v>
+      </c>
+      <c r="D321" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>188</v>
       </c>
@@ -5148,10 +7210,13 @@
         <v>327</v>
       </c>
       <c r="C322" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+      <c r="D322" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>188</v>
       </c>
@@ -5159,10 +7224,13 @@
         <v>327</v>
       </c>
       <c r="C323" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+      <c r="D323" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>188</v>
       </c>
@@ -5170,10 +7238,13 @@
         <v>327</v>
       </c>
       <c r="C324" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+      <c r="D324" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>188</v>
       </c>
@@ -5181,10 +7252,13 @@
         <v>327</v>
       </c>
       <c r="C325" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+      <c r="D325" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>188</v>
       </c>
@@ -5192,21 +7266,27 @@
         <v>327</v>
       </c>
       <c r="C326" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+      <c r="D326" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>188</v>
+        <v>2</v>
       </c>
       <c r="B327" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C327" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+      <c r="D327" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>2</v>
       </c>
@@ -5214,10 +7294,13 @@
         <v>348</v>
       </c>
       <c r="C328" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+      <c r="D328" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>2</v>
       </c>
@@ -5225,10 +7308,13 @@
         <v>348</v>
       </c>
       <c r="C329" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+      <c r="D329" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>2</v>
       </c>
@@ -5236,10 +7322,13 @@
         <v>348</v>
       </c>
       <c r="C330" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+      <c r="D330" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>2</v>
       </c>
@@ -5247,10 +7336,13 @@
         <v>348</v>
       </c>
       <c r="C331" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+      <c r="D331" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>2</v>
       </c>
@@ -5258,10 +7350,13 @@
         <v>348</v>
       </c>
       <c r="C332" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+      <c r="D332" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>2</v>
       </c>
@@ -5269,10 +7364,13 @@
         <v>348</v>
       </c>
       <c r="C333" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+      <c r="D333" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>2</v>
       </c>
@@ -5280,10 +7378,13 @@
         <v>348</v>
       </c>
       <c r="C334" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+      <c r="D334" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>2</v>
       </c>
@@ -5291,10 +7392,13 @@
         <v>348</v>
       </c>
       <c r="C335" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+      <c r="D335" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>2</v>
       </c>
@@ -5302,10 +7406,13 @@
         <v>348</v>
       </c>
       <c r="C336" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+      <c r="D336" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>2</v>
       </c>
@@ -5313,10 +7420,13 @@
         <v>348</v>
       </c>
       <c r="C337" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+      <c r="D337" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>2</v>
       </c>
@@ -5324,10 +7434,13 @@
         <v>348</v>
       </c>
       <c r="C338" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+      <c r="D338" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>2</v>
       </c>
@@ -5335,10 +7448,13 @@
         <v>348</v>
       </c>
       <c r="C339" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+      <c r="D339" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>2</v>
       </c>
@@ -5346,10 +7462,13 @@
         <v>348</v>
       </c>
       <c r="C340" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+      <c r="D340" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>2</v>
       </c>
@@ -5357,10 +7476,13 @@
         <v>348</v>
       </c>
       <c r="C341" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+      <c r="D341" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>2</v>
       </c>
@@ -5368,10 +7490,13 @@
         <v>348</v>
       </c>
       <c r="C342" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+      <c r="D342" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>2</v>
       </c>
@@ -5379,21 +7504,27 @@
         <v>348</v>
       </c>
       <c r="C343" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+      <c r="D343" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>2</v>
       </c>
       <c r="B344" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="C344" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+      <c r="D344" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>2</v>
       </c>
@@ -5401,10 +7532,13 @@
         <v>366</v>
       </c>
       <c r="C345" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+      <c r="D345" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>2</v>
       </c>
@@ -5412,10 +7546,13 @@
         <v>366</v>
       </c>
       <c r="C346" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="D346" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>2</v>
       </c>
@@ -5423,10 +7560,13 @@
         <v>366</v>
       </c>
       <c r="C347" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+      <c r="D347" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>2</v>
       </c>
@@ -5434,10 +7574,13 @@
         <v>366</v>
       </c>
       <c r="C348" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+      <c r="D348" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>2</v>
       </c>
@@ -5445,10 +7588,13 @@
         <v>366</v>
       </c>
       <c r="C349" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+      <c r="D349" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>2</v>
       </c>
@@ -5456,10 +7602,13 @@
         <v>366</v>
       </c>
       <c r="C350" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+      <c r="D350" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>2</v>
       </c>
@@ -5467,10 +7616,13 @@
         <v>366</v>
       </c>
       <c r="C351" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+      <c r="D351" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>2</v>
       </c>
@@ -5478,10 +7630,13 @@
         <v>366</v>
       </c>
       <c r="C352" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+      <c r="D352" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>2</v>
       </c>
@@ -5489,10 +7644,13 @@
         <v>366</v>
       </c>
       <c r="C353" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+      <c r="D353" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>2</v>
       </c>
@@ -5500,10 +7658,13 @@
         <v>366</v>
       </c>
       <c r="C354" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+      <c r="D354" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>2</v>
       </c>
@@ -5511,10 +7672,13 @@
         <v>366</v>
       </c>
       <c r="C355" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+      <c r="D355" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>2</v>
       </c>
@@ -5522,21 +7686,27 @@
         <v>366</v>
       </c>
       <c r="C356" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+      <c r="D356" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B357" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="C357" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+      <c r="D357" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>17</v>
       </c>
@@ -5544,10 +7714,13 @@
         <v>380</v>
       </c>
       <c r="C358" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+      <c r="D358" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>17</v>
       </c>
@@ -5555,10 +7728,13 @@
         <v>380</v>
       </c>
       <c r="C359" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+      <c r="D359" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>17</v>
       </c>
@@ -5566,10 +7742,13 @@
         <v>380</v>
       </c>
       <c r="C360" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+      <c r="D360" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>17</v>
       </c>
@@ -5577,10 +7756,13 @@
         <v>380</v>
       </c>
       <c r="C361" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+      <c r="D361" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>17</v>
       </c>
@@ -5588,10 +7770,13 @@
         <v>380</v>
       </c>
       <c r="C362" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="D362" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>17</v>
       </c>
@@ -5599,10 +7784,13 @@
         <v>380</v>
       </c>
       <c r="C363" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+      <c r="D363" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>17</v>
       </c>
@@ -5610,10 +7798,13 @@
         <v>380</v>
       </c>
       <c r="C364" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+      <c r="D364" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>17</v>
       </c>
@@ -5621,10 +7812,13 @@
         <v>380</v>
       </c>
       <c r="C365" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+      <c r="D365" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>17</v>
       </c>
@@ -5632,10 +7826,13 @@
         <v>380</v>
       </c>
       <c r="C366" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+      <c r="D366" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>17</v>
       </c>
@@ -5643,10 +7840,13 @@
         <v>380</v>
       </c>
       <c r="C367" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+      <c r="D367" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>17</v>
       </c>
@@ -5654,10 +7854,13 @@
         <v>380</v>
       </c>
       <c r="C368" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+      <c r="D368" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>17</v>
       </c>
@@ -5665,10 +7868,13 @@
         <v>380</v>
       </c>
       <c r="C369" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="D369" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>17</v>
       </c>
@@ -5676,10 +7882,13 @@
         <v>380</v>
       </c>
       <c r="C370" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+      <c r="D370" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>17</v>
       </c>
@@ -5687,10 +7896,13 @@
         <v>380</v>
       </c>
       <c r="C371" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+      <c r="D371" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>17</v>
       </c>
@@ -5698,32 +7910,14 @@
         <v>380</v>
       </c>
       <c r="C372" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A373" t="s">
-        <v>17</v>
-      </c>
-      <c r="B373" t="s">
-        <v>380</v>
-      </c>
-      <c r="C373" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A374">
-        <v>0</v>
-      </c>
-      <c r="B374">
-        <v>0</v>
-      </c>
-      <c r="C374">
-        <v>0</v>
+      <c r="D372" t="s">
+        <v>732</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D372" xr:uid="{6A3A076C-ECA7-4854-BDDC-C813E3A40233}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Facilities.xlsx
+++ b/Facilities.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chinedu\Documents\GitHub\SOH-TRACKER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2326E0C5-CB43-4317-8442-FCB3AFF915C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62186D6-E1FD-4225-8B12-91F291FE9D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{894FD31D-B550-4319-A669-590A5406D934}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$372</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$372</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="1454">
   <si>
     <t>Cluster</t>
   </si>
@@ -2331,6 +2331,2076 @@
   </si>
   <si>
     <t>NzwdCUPjLKM</t>
+  </si>
+  <si>
+    <t>OldDPT Orgunitid</t>
+  </si>
+  <si>
+    <t>IHVN Orgunitid</t>
+  </si>
+  <si>
+    <t>Fuc0tYAWnay</t>
+  </si>
+  <si>
+    <t>CMDJRAXQ3JJ</t>
+  </si>
+  <si>
+    <t>iYOEvWWuuHt</t>
+  </si>
+  <si>
+    <t>XjJTeqU0oTR</t>
+  </si>
+  <si>
+    <t>pL0aZwWa2Wn</t>
+  </si>
+  <si>
+    <t>a4yROKQkxFB</t>
+  </si>
+  <si>
+    <t>T84f4kPXe67</t>
+  </si>
+  <si>
+    <t>tKayEULPMjD</t>
+  </si>
+  <si>
+    <t>oDSiCLxRGkH</t>
+  </si>
+  <si>
+    <t>uDmr747BVUL</t>
+  </si>
+  <si>
+    <t>Em2TnmA8okG</t>
+  </si>
+  <si>
+    <t>Bt9VX1VFDxa</t>
+  </si>
+  <si>
+    <t>sGGftk2lgV7</t>
+  </si>
+  <si>
+    <t>o9KyVBh2udc</t>
+  </si>
+  <si>
+    <t>kz2DfO8w25S</t>
+  </si>
+  <si>
+    <t>g06Cjhg0Nx0</t>
+  </si>
+  <si>
+    <t>w3DAwIxUybW</t>
+  </si>
+  <si>
+    <t>u6BFtuYC3N6</t>
+  </si>
+  <si>
+    <t>XBykIPX39lp</t>
+  </si>
+  <si>
+    <t>krk0wHwxF8K</t>
+  </si>
+  <si>
+    <t>GPNbryAytbc</t>
+  </si>
+  <si>
+    <t>H9nF79RMIuV</t>
+  </si>
+  <si>
+    <t>Z1iJXwwNFTe</t>
+  </si>
+  <si>
+    <t>h6f7ImyB1SG</t>
+  </si>
+  <si>
+    <t>NY86yBt1ode</t>
+  </si>
+  <si>
+    <t>he4QHMq5kWl</t>
+  </si>
+  <si>
+    <t>fBN0tquSgoF</t>
+  </si>
+  <si>
+    <t>LU59s2r4VWo</t>
+  </si>
+  <si>
+    <t>iu7X0R8lnGw</t>
+  </si>
+  <si>
+    <t>mdY6unLiE6B</t>
+  </si>
+  <si>
+    <t>x3VCYBqlg6D</t>
+  </si>
+  <si>
+    <t>fqAHWgccY0w</t>
+  </si>
+  <si>
+    <t>nzGm85Cnv9J</t>
+  </si>
+  <si>
+    <t>c9Y5m1waVDT</t>
+  </si>
+  <si>
+    <t>Keq00q3BPSz</t>
+  </si>
+  <si>
+    <t>mmtEdjGfM3Q</t>
+  </si>
+  <si>
+    <t>fUC3IZQ0UDN</t>
+  </si>
+  <si>
+    <t>lCPH8TZkXat</t>
+  </si>
+  <si>
+    <t>ztAqSeYb9hG</t>
+  </si>
+  <si>
+    <t>UKbo5pglm0s</t>
+  </si>
+  <si>
+    <t>E1BPEY3tbLd</t>
+  </si>
+  <si>
+    <t>sIy8dYAfFId</t>
+  </si>
+  <si>
+    <t>C69kC1jqTuc</t>
+  </si>
+  <si>
+    <t>SFJ48xqZFzL</t>
+  </si>
+  <si>
+    <t>NHxMtWobfEG</t>
+  </si>
+  <si>
+    <t>H4FwzwDkV59</t>
+  </si>
+  <si>
+    <t>d6mAEvpsmcl</t>
+  </si>
+  <si>
+    <t>lAIvYqbcsa5</t>
+  </si>
+  <si>
+    <t>QtposFiqmeI</t>
+  </si>
+  <si>
+    <t>Z4zzttqqGrc</t>
+  </si>
+  <si>
+    <t>O7L6lbpbsuP</t>
+  </si>
+  <si>
+    <t>c2lWNSLqjdI</t>
+  </si>
+  <si>
+    <t>sds6algE1pi</t>
+  </si>
+  <si>
+    <t>h46m6IwZtg2</t>
+  </si>
+  <si>
+    <t>HMIBLCySlvz</t>
+  </si>
+  <si>
+    <t>MRk46YAigTd</t>
+  </si>
+  <si>
+    <t>pQpi7RiNdSE</t>
+  </si>
+  <si>
+    <t>QvlRvN7RLUe</t>
+  </si>
+  <si>
+    <t>wZdOVwO1k6q</t>
+  </si>
+  <si>
+    <t>kieG1WrNILu</t>
+  </si>
+  <si>
+    <t>HZwMNdKSft8</t>
+  </si>
+  <si>
+    <t>N92KEeGVAqm</t>
+  </si>
+  <si>
+    <t>ZjUUKZCy41c</t>
+  </si>
+  <si>
+    <t>pqAJ8m78W2Z</t>
+  </si>
+  <si>
+    <t>PG5VSy9iG7M</t>
+  </si>
+  <si>
+    <t>ITyf9JDmpDR</t>
+  </si>
+  <si>
+    <t>mF2mFtGG0Uu</t>
+  </si>
+  <si>
+    <t>ivkmsXXLTGx</t>
+  </si>
+  <si>
+    <t>A1RGJelaUOI</t>
+  </si>
+  <si>
+    <t>JqE53zvGjGi</t>
+  </si>
+  <si>
+    <t>EoOCVAZKmWP</t>
+  </si>
+  <si>
+    <t>BjfxEPMoC03</t>
+  </si>
+  <si>
+    <t>eG5s3FDMsjn</t>
+  </si>
+  <si>
+    <t>jV2HGFgNqll</t>
+  </si>
+  <si>
+    <t>lrdlD8nyz9p</t>
+  </si>
+  <si>
+    <t>sA7v8Xy4EIc</t>
+  </si>
+  <si>
+    <t>auLjMOOWlX8</t>
+  </si>
+  <si>
+    <t>GPN9NHnZlE7</t>
+  </si>
+  <si>
+    <t>ejZZspIfDXr</t>
+  </si>
+  <si>
+    <t>sKN6KkFAdt7</t>
+  </si>
+  <si>
+    <t>yS3nwIRyjio</t>
+  </si>
+  <si>
+    <t>F2UxZsPkKYP</t>
+  </si>
+  <si>
+    <t>zFGL2cIk55r</t>
+  </si>
+  <si>
+    <t>ppvtkzFnSgN</t>
+  </si>
+  <si>
+    <t>LtZNfzSSoX6</t>
+  </si>
+  <si>
+    <t>HVJdwqktbLT</t>
+  </si>
+  <si>
+    <t>XSuiktsbAgq</t>
+  </si>
+  <si>
+    <t>zB2rbQTuzk8</t>
+  </si>
+  <si>
+    <t>kl8HKjrUYp1</t>
+  </si>
+  <si>
+    <t>oi3lUOeL1bB</t>
+  </si>
+  <si>
+    <t>MeJASB3Wayb</t>
+  </si>
+  <si>
+    <t>Hzm1UPHaIrC</t>
+  </si>
+  <si>
+    <t>WnptmFFb094</t>
+  </si>
+  <si>
+    <t>h7q9k2u2DMg</t>
+  </si>
+  <si>
+    <t>uaZVftdZCXq</t>
+  </si>
+  <si>
+    <t>pPKPR5bGrY7</t>
+  </si>
+  <si>
+    <t>wNSmpuvLvDC</t>
+  </si>
+  <si>
+    <t>bYNnT4jy2BK</t>
+  </si>
+  <si>
+    <t>rqCdYpI56Uq</t>
+  </si>
+  <si>
+    <t>nuPFmMApX3G</t>
+  </si>
+  <si>
+    <t>cV2Cte4uF2p</t>
+  </si>
+  <si>
+    <t>ANfYWSzOoGC</t>
+  </si>
+  <si>
+    <t>nm9G7kFCkvn</t>
+  </si>
+  <si>
+    <t>COFcCs1F9el</t>
+  </si>
+  <si>
+    <t>BVZYBWBOS82</t>
+  </si>
+  <si>
+    <t>OK7ngDjbzbi</t>
+  </si>
+  <si>
+    <t>yd3SVdRUTgb</t>
+  </si>
+  <si>
+    <t>zexA6lx7Asd</t>
+  </si>
+  <si>
+    <t>Sn3wlzxnMOn</t>
+  </si>
+  <si>
+    <t>oWJPrMEkddF</t>
+  </si>
+  <si>
+    <t>Zj2tFLyuiGP</t>
+  </si>
+  <si>
+    <t>dRv98vS7QCo</t>
+  </si>
+  <si>
+    <t>zXIIlBvhxv0</t>
+  </si>
+  <si>
+    <t>gZ2RozoBzrK</t>
+  </si>
+  <si>
+    <t>RL5ZypHWIDK</t>
+  </si>
+  <si>
+    <t>QZhmYMTtmTM</t>
+  </si>
+  <si>
+    <t>Ob1cSMb9tYS</t>
+  </si>
+  <si>
+    <t>nJuYO8i4RAn</t>
+  </si>
+  <si>
+    <t>iHydWbDXbUE</t>
+  </si>
+  <si>
+    <t>sgnGmDDn1ki</t>
+  </si>
+  <si>
+    <t>JWl3pSy9qS0</t>
+  </si>
+  <si>
+    <t>xrXrfVj9Uta</t>
+  </si>
+  <si>
+    <t>w9OG5Mjf9vF</t>
+  </si>
+  <si>
+    <t>O1GH9KiOP3d</t>
+  </si>
+  <si>
+    <t>uyFiGqmgj4T</t>
+  </si>
+  <si>
+    <t>phXAKROepIJ</t>
+  </si>
+  <si>
+    <t>tWLO3iPTQhB</t>
+  </si>
+  <si>
+    <t>MV64CjzYcWs</t>
+  </si>
+  <si>
+    <t>D5t3EwZPuVP</t>
+  </si>
+  <si>
+    <t>vHClNOOg5NL</t>
+  </si>
+  <si>
+    <t>otkyQCBGlP9</t>
+  </si>
+  <si>
+    <t>ZxNmPOIGDrb</t>
+  </si>
+  <si>
+    <t>Dj26RXvh8tk</t>
+  </si>
+  <si>
+    <t>FpJNxhEoFZP</t>
+  </si>
+  <si>
+    <t>LzlcL6RQe8T</t>
+  </si>
+  <si>
+    <t>wy3RbpE5Ti6</t>
+  </si>
+  <si>
+    <t>uZthAyFByCF</t>
+  </si>
+  <si>
+    <t>p9uBIH33Ql0</t>
+  </si>
+  <si>
+    <t>Fdu06AIrVUJ</t>
+  </si>
+  <si>
+    <t>EaACF3PiC4B</t>
+  </si>
+  <si>
+    <t>YcGQAnhdaJs</t>
+  </si>
+  <si>
+    <t>bDxXXmognkF</t>
+  </si>
+  <si>
+    <t>oSDSKIX6Mwj</t>
+  </si>
+  <si>
+    <t>vUwdQ8Rfi4B</t>
+  </si>
+  <si>
+    <t>oHIGz4Thj5q</t>
+  </si>
+  <si>
+    <t>ygrVmL1WuVy</t>
+  </si>
+  <si>
+    <t>cuzH18f5Muv</t>
+  </si>
+  <si>
+    <t>fu6V5RaQsMb</t>
+  </si>
+  <si>
+    <t>IaEWbfqCVmz</t>
+  </si>
+  <si>
+    <t>FQes2ePjAlH</t>
+  </si>
+  <si>
+    <t>gfKsnHEVp5u</t>
+  </si>
+  <si>
+    <t>aMP0PF59sxj</t>
+  </si>
+  <si>
+    <t>f9pDrbE5tOU</t>
+  </si>
+  <si>
+    <t>MnkQELP9Mw9</t>
+  </si>
+  <si>
+    <t>FCoO4ECGslQ</t>
+  </si>
+  <si>
+    <t>zB7Nssjl1j4</t>
+  </si>
+  <si>
+    <t>Tz2HQ6mTseq</t>
+  </si>
+  <si>
+    <t>KbBMhO1zQZN</t>
+  </si>
+  <si>
+    <t>BKtNXtbPgaM</t>
+  </si>
+  <si>
+    <t>bTY0wzPCZmS</t>
+  </si>
+  <si>
+    <t>zQi4k8l95xk</t>
+  </si>
+  <si>
+    <t>uA6xWRVbtRa</t>
+  </si>
+  <si>
+    <t>aruF6LHYZ6L</t>
+  </si>
+  <si>
+    <t>igLZxGz2WWX</t>
+  </si>
+  <si>
+    <t>MPfqeRWR7wD</t>
+  </si>
+  <si>
+    <t>TXRIDxg9oM0</t>
+  </si>
+  <si>
+    <t>zbrgtyAO021</t>
+  </si>
+  <si>
+    <t>Y5a9w4dU23r</t>
+  </si>
+  <si>
+    <t>cangYYIBfRO</t>
+  </si>
+  <si>
+    <t>pUAqyTfohCq</t>
+  </si>
+  <si>
+    <t>SztyXJb5t2I</t>
+  </si>
+  <si>
+    <t>jdS64PWRLmj</t>
+  </si>
+  <si>
+    <t>MEbX7vtq4EB</t>
+  </si>
+  <si>
+    <t>vELUmbXqS9I</t>
+  </si>
+  <si>
+    <t>Id2X54Vylx3</t>
+  </si>
+  <si>
+    <t>tiykwgstzMo</t>
+  </si>
+  <si>
+    <t>z3E5z6QsnIk</t>
+  </si>
+  <si>
+    <t>M5EcgsZvO8F</t>
+  </si>
+  <si>
+    <t>RtyrQeNRGPc</t>
+  </si>
+  <si>
+    <t>A7DVlN3Qr74</t>
+  </si>
+  <si>
+    <t>xeVoYpEZr8y</t>
+  </si>
+  <si>
+    <t>PotoATIeHZP</t>
+  </si>
+  <si>
+    <t>HpM3L3cYL3J</t>
+  </si>
+  <si>
+    <t>IgjWv5xibFn</t>
+  </si>
+  <si>
+    <t>T0rJjY5rJK0</t>
+  </si>
+  <si>
+    <t>NoQzGRiZSFT</t>
+  </si>
+  <si>
+    <t>E7YYa1DNBD9</t>
+  </si>
+  <si>
+    <t>trWKBij5oso</t>
+  </si>
+  <si>
+    <t>kOOcW5oNbji</t>
+  </si>
+  <si>
+    <t>rbIL0XhIfEV</t>
+  </si>
+  <si>
+    <t>aTjgGhWkwWy</t>
+  </si>
+  <si>
+    <t>dM6kioII6hn</t>
+  </si>
+  <si>
+    <t>BJyIYLLysRw</t>
+  </si>
+  <si>
+    <t>jsdd6MCTaGK</t>
+  </si>
+  <si>
+    <t>eKLUu519plE</t>
+  </si>
+  <si>
+    <t>h8A5Oy09ulR</t>
+  </si>
+  <si>
+    <t>z4TbD4jEEBC</t>
+  </si>
+  <si>
+    <t>ovsIQaTQcnX</t>
+  </si>
+  <si>
+    <t>NmvJV7Ybxky</t>
+  </si>
+  <si>
+    <t>qpKZFr5fnUJ</t>
+  </si>
+  <si>
+    <t>Ir4A2o8EiZH</t>
+  </si>
+  <si>
+    <t>qfy9JLZmpYx</t>
+  </si>
+  <si>
+    <t>ofc3TnJ23FW</t>
+  </si>
+  <si>
+    <t>kE7NeU9jiQZ</t>
+  </si>
+  <si>
+    <t>TNt7tlpIFfJ</t>
+  </si>
+  <si>
+    <t>frhFCneyeUO</t>
+  </si>
+  <si>
+    <t>uJEB7mX2oXU</t>
+  </si>
+  <si>
+    <t>RNMzJhONPVh</t>
+  </si>
+  <si>
+    <t>E8ATy58mNf5</t>
+  </si>
+  <si>
+    <t>l4IGRCOU8Ac</t>
+  </si>
+  <si>
+    <t>t5kKjdEYkwu</t>
+  </si>
+  <si>
+    <t>TMS2bKBkLG9</t>
+  </si>
+  <si>
+    <t>D2pBPDq03fg</t>
+  </si>
+  <si>
+    <t>Ums6Q9wIGEh</t>
+  </si>
+  <si>
+    <t>uA4t4LbnrXg</t>
+  </si>
+  <si>
+    <t>oz7eXDo27Nv</t>
+  </si>
+  <si>
+    <t>hEfTWuBQJrh</t>
+  </si>
+  <si>
+    <t>TwLuy4eMFcn</t>
+  </si>
+  <si>
+    <t>C8s0krJf4vM</t>
+  </si>
+  <si>
+    <t>wUsJkeInU4v</t>
+  </si>
+  <si>
+    <t>uWPi6aRQNKj</t>
+  </si>
+  <si>
+    <t>beBO9nDt5fb</t>
+  </si>
+  <si>
+    <t>POzJpHUNsbl</t>
+  </si>
+  <si>
+    <t>kLZ58TpqmFn</t>
+  </si>
+  <si>
+    <t>dfAqyJer0dh</t>
+  </si>
+  <si>
+    <t>aJKdzQsswLi</t>
+  </si>
+  <si>
+    <t>DAEnK7KTk5H</t>
+  </si>
+  <si>
+    <t>IrkQjZQIToI</t>
+  </si>
+  <si>
+    <t>I3olgTszSEp</t>
+  </si>
+  <si>
+    <t>gbQi7qnCKTZ</t>
+  </si>
+  <si>
+    <t>Ced1DGpgPh1</t>
+  </si>
+  <si>
+    <t>DHJOPYI6S01</t>
+  </si>
+  <si>
+    <t>gBa3vU9LlbZ</t>
+  </si>
+  <si>
+    <t>KUiS3gmX1EW</t>
+  </si>
+  <si>
+    <t>Tw7E7LbxKZp</t>
+  </si>
+  <si>
+    <t>gBc3sxoZ8Nx</t>
+  </si>
+  <si>
+    <t>x0B56IGimVc</t>
+  </si>
+  <si>
+    <t>tMtV5YRK8Wv</t>
+  </si>
+  <si>
+    <t>uORzff3z8el</t>
+  </si>
+  <si>
+    <t>HWDM3Phntnn</t>
+  </si>
+  <si>
+    <t>tdIgDgFzTfe</t>
+  </si>
+  <si>
+    <t>cOYbPyHCHrY</t>
+  </si>
+  <si>
+    <t>IUCe0tB8CQo</t>
+  </si>
+  <si>
+    <t>GO9mtFJTuOj</t>
+  </si>
+  <si>
+    <t>HtLBS7zqBnL</t>
+  </si>
+  <si>
+    <t>Bm7RGF67wSl</t>
+  </si>
+  <si>
+    <t>VOt7euM2ZXB</t>
+  </si>
+  <si>
+    <t>vzMWHF2x902</t>
+  </si>
+  <si>
+    <t>RmGiuoKavek</t>
+  </si>
+  <si>
+    <t>x4MDe9tGJU0</t>
+  </si>
+  <si>
+    <t>S9VfZotFtRG</t>
+  </si>
+  <si>
+    <t>emM0wlRfMy3</t>
+  </si>
+  <si>
+    <t>cZUT6ioFtS2</t>
+  </si>
+  <si>
+    <t>gR6urEagkTe</t>
+  </si>
+  <si>
+    <t>igisSOXuobY</t>
+  </si>
+  <si>
+    <t>JQavCYNg0DF</t>
+  </si>
+  <si>
+    <t>zx9JRrEMxrW</t>
+  </si>
+  <si>
+    <t>VhiJ8IV80XZ</t>
+  </si>
+  <si>
+    <t>RuX6DN3lkDt</t>
+  </si>
+  <si>
+    <t>ChT9fXzVLUp</t>
+  </si>
+  <si>
+    <t>xB64ilfMHfq</t>
+  </si>
+  <si>
+    <t>qN8LgVcf6ce</t>
+  </si>
+  <si>
+    <t>AI9LKt8F3vv</t>
+  </si>
+  <si>
+    <t>Y9DJltgM7Ki</t>
+  </si>
+  <si>
+    <t>hGrKXISLp9t</t>
+  </si>
+  <si>
+    <t>g24BX4Kroq2</t>
+  </si>
+  <si>
+    <t>nBOIHGRHWRM</t>
+  </si>
+  <si>
+    <t>Z8lJKvwfVjR</t>
+  </si>
+  <si>
+    <t>wQSlorPTFPQ</t>
+  </si>
+  <si>
+    <t>LqjqXAYKO3U</t>
+  </si>
+  <si>
+    <t>An3fHhEE9mq</t>
+  </si>
+  <si>
+    <t>JyKrMZR8xxN</t>
+  </si>
+  <si>
+    <t>S0whJZigotz</t>
+  </si>
+  <si>
+    <t>l8rJ5e48jMr</t>
+  </si>
+  <si>
+    <t>o3r8L1r5CXK</t>
+  </si>
+  <si>
+    <t>jveLUpB5fpu</t>
+  </si>
+  <si>
+    <t>FNhMALEsdWV</t>
+  </si>
+  <si>
+    <t>YYy2q6v3IoA</t>
+  </si>
+  <si>
+    <t>fHPiYOUoy0i</t>
+  </si>
+  <si>
+    <t>HsyrYhO3wjo</t>
+  </si>
+  <si>
+    <t>A02OG4IpKof</t>
+  </si>
+  <si>
+    <t>q1JUZz1nFnT</t>
+  </si>
+  <si>
+    <t>ZwdDIsThRkB</t>
+  </si>
+  <si>
+    <t>PaBSYMDzilh</t>
+  </si>
+  <si>
+    <t>pJTkXD7D0K4</t>
+  </si>
+  <si>
+    <t>cn3rFJjkGWg</t>
+  </si>
+  <si>
+    <t>U5SGKxaLDBZ</t>
+  </si>
+  <si>
+    <t>EogABqEXLmM</t>
+  </si>
+  <si>
+    <t>BGiIb45Ddb7</t>
+  </si>
+  <si>
+    <t>mZZivtWzOM1</t>
+  </si>
+  <si>
+    <t>JNzz4Ot5wOv</t>
+  </si>
+  <si>
+    <t>GSbZR076AIt</t>
+  </si>
+  <si>
+    <t>yJLTk5jUOwb</t>
+  </si>
+  <si>
+    <t>dRwiOcEt6VZ</t>
+  </si>
+  <si>
+    <t>RF8Agg39MSf</t>
+  </si>
+  <si>
+    <t>vcEyfKdcfDL</t>
+  </si>
+  <si>
+    <t>qZyQcI16qmo</t>
+  </si>
+  <si>
+    <t>pn3FvtoqjBU</t>
+  </si>
+  <si>
+    <t>VrhLYyDfjyu</t>
+  </si>
+  <si>
+    <t>pt1GpBfga14</t>
+  </si>
+  <si>
+    <t>PsZYMuWLoBi</t>
+  </si>
+  <si>
+    <t>b9uajGDHB5l</t>
+  </si>
+  <si>
+    <t>KGU8ohMHE2b</t>
+  </si>
+  <si>
+    <t>A6w7pcCtq3W</t>
+  </si>
+  <si>
+    <t>UwLDGtCfQ2P</t>
+  </si>
+  <si>
+    <t>OLBQIcNoGUw</t>
+  </si>
+  <si>
+    <t>dJ1dw3O8TzJ</t>
+  </si>
+  <si>
+    <t>d5BWdABIbzZ</t>
+  </si>
+  <si>
+    <t>SB6L9nfSTdT</t>
+  </si>
+  <si>
+    <t>tcrTMifLqU0</t>
+  </si>
+  <si>
+    <t>Txc3MIIwob4</t>
+  </si>
+  <si>
+    <t>BzZsjauaBQe</t>
+  </si>
+  <si>
+    <t>DrBIEqVuzKQ</t>
+  </si>
+  <si>
+    <t>Hku3gH1gBs1</t>
+  </si>
+  <si>
+    <t>JzsJn22e7fx</t>
+  </si>
+  <si>
+    <t>xk2BkAN5PU6</t>
+  </si>
+  <si>
+    <t>ipJsMIVTXyb</t>
+  </si>
+  <si>
+    <t>G9YExyUDqvY</t>
+  </si>
+  <si>
+    <t>KLd1BpkzfEn</t>
+  </si>
+  <si>
+    <t>eQtembRmiJa</t>
+  </si>
+  <si>
+    <t>WYPGVR17N8P</t>
+  </si>
+  <si>
+    <t>ej1C5qv35Vf</t>
+  </si>
+  <si>
+    <t>JUYhIsfkt8K</t>
+  </si>
+  <si>
+    <t>IOvDLinckdB</t>
+  </si>
+  <si>
+    <t>vQ0B5mvMOVq</t>
+  </si>
+  <si>
+    <t>JTo5vubzNg9</t>
+  </si>
+  <si>
+    <t>T7jVyoIL7lj</t>
+  </si>
+  <si>
+    <t>PDq1hTvxjDI</t>
+  </si>
+  <si>
+    <t>rBYfdXIYxUr</t>
+  </si>
+  <si>
+    <t>bqURBx4dqkZ</t>
+  </si>
+  <si>
+    <t>d7DtKuTOfHm</t>
+  </si>
+  <si>
+    <t>N0q0P02ZexO</t>
+  </si>
+  <si>
+    <t>NGWDqMRYGO7</t>
+  </si>
+  <si>
+    <t>MoYFQXQF1Nd</t>
+  </si>
+  <si>
+    <t>DxmIhrch9em</t>
+  </si>
+  <si>
+    <t>LyLPAvTjmei</t>
+  </si>
+  <si>
+    <t>pMFO7YwHpNR</t>
+  </si>
+  <si>
+    <t>DAyLBcNkr6S</t>
+  </si>
+  <si>
+    <t>mfQsiwi3ph5</t>
+  </si>
+  <si>
+    <t>ANoAlUUC4fN</t>
+  </si>
+  <si>
+    <t>zRZuEVNRHyv</t>
+  </si>
+  <si>
+    <t>cja27ienhZ3</t>
+  </si>
+  <si>
+    <t>owJNdbTnCTZ</t>
+  </si>
+  <si>
+    <t>McrEU2tJDxG</t>
+  </si>
+  <si>
+    <t>v4jEdr5lpFw</t>
+  </si>
+  <si>
+    <t>cMS2xK8hKco</t>
+  </si>
+  <si>
+    <t>yd20NTVw7jD</t>
+  </si>
+  <si>
+    <t>JB0PE5muWMy</t>
+  </si>
+  <si>
+    <t>jusNKGYYiXh</t>
+  </si>
+  <si>
+    <t>GMobsBHkB19</t>
+  </si>
+  <si>
+    <t>wKoC39IjQj4</t>
+  </si>
+  <si>
+    <t>HGfogcZP3x5</t>
+  </si>
+  <si>
+    <t>kqTaLVrcsC5</t>
+  </si>
+  <si>
+    <t>AQyD5PfXQPF</t>
+  </si>
+  <si>
+    <t>fIaWzo6oZzQ</t>
+  </si>
+  <si>
+    <t>wLBEwYkHHH7</t>
+  </si>
+  <si>
+    <t>mV5lsyZGumf</t>
+  </si>
+  <si>
+    <t>dUxg8YJt4FJ</t>
+  </si>
+  <si>
+    <t>VXxdTX6pIUT</t>
+  </si>
+  <si>
+    <t>BA4Wc23seEl</t>
+  </si>
+  <si>
+    <t>H5mrenVQD4o</t>
+  </si>
+  <si>
+    <t>YWxHDFJiLgW</t>
+  </si>
+  <si>
+    <t>Hg9qT27VXDt</t>
+  </si>
+  <si>
+    <t>FXGCzzjjMto</t>
+  </si>
+  <si>
+    <t>AvCFER990jd</t>
+  </si>
+  <si>
+    <t>voRu867alOR</t>
+  </si>
+  <si>
+    <t>hP1G9AtXeB9</t>
+  </si>
+  <si>
+    <t>sd6gLvBlRwe</t>
+  </si>
+  <si>
+    <t>DJUlzoPUGGy</t>
+  </si>
+  <si>
+    <t>o6rZq8VYVHV</t>
+  </si>
+  <si>
+    <t>LYOsIVWjBFZ</t>
+  </si>
+  <si>
+    <t>pNznwh9aSWk</t>
+  </si>
+  <si>
+    <t>rMwMFWNiqKx</t>
+  </si>
+  <si>
+    <t>L8a5gfRNYqj</t>
+  </si>
+  <si>
+    <t>ROMZK7BwlCS</t>
+  </si>
+  <si>
+    <t>vnR92IA0EYr</t>
+  </si>
+  <si>
+    <t>p6b5M5Ztssi</t>
+  </si>
+  <si>
+    <t>m0Vh9sAfutU</t>
+  </si>
+  <si>
+    <t>SnWyEN4EKi3</t>
+  </si>
+  <si>
+    <t>lg8GwVSSmIt</t>
+  </si>
+  <si>
+    <t>tzhJlLaueN9</t>
+  </si>
+  <si>
+    <t>VYhXB922NIf</t>
+  </si>
+  <si>
+    <t>jIhv4K1LVuT</t>
+  </si>
+  <si>
+    <t>UjKcOpy69tb</t>
+  </si>
+  <si>
+    <t>hBlxbWNyMRP</t>
+  </si>
+  <si>
+    <t>u7WQNfxPIxW</t>
+  </si>
+  <si>
+    <t>g6Ijia1TshK</t>
+  </si>
+  <si>
+    <t>AkyGysExEcA</t>
+  </si>
+  <si>
+    <t>DtS7u40js6a</t>
+  </si>
+  <si>
+    <t>JXXeEu8MTGP</t>
+  </si>
+  <si>
+    <t>eB7wawgBqBa</t>
+  </si>
+  <si>
+    <t>bkXKnd9yI6T</t>
+  </si>
+  <si>
+    <t>xLB2qxsZjDe</t>
+  </si>
+  <si>
+    <t>YmRyt9k0Q4S</t>
+  </si>
+  <si>
+    <t>u2sZcRzNOfJ</t>
+  </si>
+  <si>
+    <t>TFPNesvGaYN</t>
+  </si>
+  <si>
+    <t>pjCVCtfDwkG</t>
+  </si>
+  <si>
+    <t>NdTAExbnRop</t>
+  </si>
+  <si>
+    <t>bZkJycCTOGF</t>
+  </si>
+  <si>
+    <t>FqoQN5Q0tjc</t>
+  </si>
+  <si>
+    <t>hPl2F21OA3V</t>
+  </si>
+  <si>
+    <t>jsuBK41OmtW</t>
+  </si>
+  <si>
+    <t>UJOLEoJGvWB</t>
+  </si>
+  <si>
+    <t>V712X3IeJRC</t>
+  </si>
+  <si>
+    <t>K8u3adLFw5W</t>
+  </si>
+  <si>
+    <t>uzPUb9kStLn</t>
+  </si>
+  <si>
+    <t>ho8y07ESbU9</t>
+  </si>
+  <si>
+    <t>pFjnxMujBmx</t>
+  </si>
+  <si>
+    <t>v9sOFiKa958</t>
+  </si>
+  <si>
+    <t>qWIluJtEI09</t>
+  </si>
+  <si>
+    <t>HHpno0B8Kxu</t>
+  </si>
+  <si>
+    <t>xESAcRAR2ew</t>
+  </si>
+  <si>
+    <t>cn1Ex72dbys</t>
+  </si>
+  <si>
+    <t>ICF6jXzPdgN</t>
+  </si>
+  <si>
+    <t>EcIADy5yicQ</t>
+  </si>
+  <si>
+    <t>nr78FJukEOW</t>
+  </si>
+  <si>
+    <t>fEUS4VwKLns</t>
+  </si>
+  <si>
+    <t>WzxZrlO19SY</t>
+  </si>
+  <si>
+    <t>gKg7VAvHLkc</t>
+  </si>
+  <si>
+    <t>MNjq24AKG2O</t>
+  </si>
+  <si>
+    <t>G6Y6XVrzuBV</t>
+  </si>
+  <si>
+    <t>YSbu0kyVVHs</t>
+  </si>
+  <si>
+    <t>kgGsLIQBSmu</t>
+  </si>
+  <si>
+    <t>l1oUGKkckkj</t>
+  </si>
+  <si>
+    <t>XhjnLwDMfn1</t>
+  </si>
+  <si>
+    <t>jVVU4jA3nnU</t>
+  </si>
+  <si>
+    <t>pvJOPy7oiBg</t>
+  </si>
+  <si>
+    <t>XPSdcnWKhhq</t>
+  </si>
+  <si>
+    <t>cuTp7nN5bVf</t>
+  </si>
+  <si>
+    <t>Cxx32ANPrEh</t>
+  </si>
+  <si>
+    <t>uFVZfsCjLnw</t>
+  </si>
+  <si>
+    <t>vgKUYeRs7ay</t>
+  </si>
+  <si>
+    <t>XzXU5imdrpX</t>
+  </si>
+  <si>
+    <t>VQiezvaCDKT</t>
+  </si>
+  <si>
+    <t>uFlgnbQ8LWp</t>
+  </si>
+  <si>
+    <t>pfeGM5h0eBt</t>
+  </si>
+  <si>
+    <t>XKIVrWDqvSf</t>
+  </si>
+  <si>
+    <t>D5duXVmlHip</t>
+  </si>
+  <si>
+    <t>JIeSWQswvKV</t>
+  </si>
+  <si>
+    <t>BLSoyByelhH</t>
+  </si>
+  <si>
+    <t>cR8nX3NG2p5</t>
+  </si>
+  <si>
+    <t>NqmewtnUriG</t>
+  </si>
+  <si>
+    <t>mLax2Kl32LO</t>
+  </si>
+  <si>
+    <t>Le3BL82Kf07</t>
+  </si>
+  <si>
+    <t>AokZ5xjS0El</t>
+  </si>
+  <si>
+    <t>uGgZfuovkDV</t>
+  </si>
+  <si>
+    <t>r2Hej8CZd86</t>
+  </si>
+  <si>
+    <t>MPBsnHXxxM8</t>
+  </si>
+  <si>
+    <t>PsnarwnYvTT</t>
+  </si>
+  <si>
+    <t>YVY11jEOtvx</t>
+  </si>
+  <si>
+    <t>sEjolHUoQpi</t>
+  </si>
+  <si>
+    <t>tGkNC0S2Su3</t>
+  </si>
+  <si>
+    <t>xkkXcHWFwfe</t>
+  </si>
+  <si>
+    <t>g7MY0R3s5Hk</t>
+  </si>
+  <si>
+    <t>sq7pMnbrqsQ</t>
+  </si>
+  <si>
+    <t>tUfsIODF3tX</t>
+  </si>
+  <si>
+    <t>eJD5VZKVzAk</t>
+  </si>
+  <si>
+    <t>nbOgWv1FMtp</t>
+  </si>
+  <si>
+    <t>nBvE1Ligixx</t>
+  </si>
+  <si>
+    <t>HvLhmFxoaJG</t>
+  </si>
+  <si>
+    <t>oOgGoMsdvJJ</t>
+  </si>
+  <si>
+    <t>UretpAwfXoa</t>
+  </si>
+  <si>
+    <t>COSHzKclfpn</t>
+  </si>
+  <si>
+    <t>Sqy4oaOHk9V</t>
+  </si>
+  <si>
+    <t>lEdQnTvLnER</t>
+  </si>
+  <si>
+    <t>j2ZyNOo7ODZ</t>
+  </si>
+  <si>
+    <t>yoP8OzxmfDN</t>
+  </si>
+  <si>
+    <t>kriL3ukhHlq</t>
+  </si>
+  <si>
+    <t>JbmunYDY6jl</t>
+  </si>
+  <si>
+    <t>CY0bezJoOeK</t>
+  </si>
+  <si>
+    <t>WwYLZc4fEaY</t>
+  </si>
+  <si>
+    <t>jiUDxeu6dSw</t>
+  </si>
+  <si>
+    <t>RZdB3t2gCxN</t>
+  </si>
+  <si>
+    <t>WLjAPalySSr</t>
+  </si>
+  <si>
+    <t>qQI9HpHGH4R</t>
+  </si>
+  <si>
+    <t>dnS90t1G7h0</t>
+  </si>
+  <si>
+    <t>F1YiS3PO6bk</t>
+  </si>
+  <si>
+    <t>HzVKkXQgu7D</t>
+  </si>
+  <si>
+    <t>CIiEQwVOdQP</t>
+  </si>
+  <si>
+    <t>nEtwTPVJx8P</t>
+  </si>
+  <si>
+    <t>WVXpMLAtmsh</t>
+  </si>
+  <si>
+    <t>ktJVgQt9u41</t>
+  </si>
+  <si>
+    <t>a8r3fIm1Fgf</t>
+  </si>
+  <si>
+    <t>UnZ6e0hETYZ</t>
+  </si>
+  <si>
+    <t>NSyCMknyq8J</t>
+  </si>
+  <si>
+    <t>FD58kgKJF7g</t>
+  </si>
+  <si>
+    <t>UPcELXvKTlp</t>
+  </si>
+  <si>
+    <t>uKVWADHygyN</t>
+  </si>
+  <si>
+    <t>ggeG6d44zAi</t>
+  </si>
+  <si>
+    <t>WonDWLmmTcJ</t>
+  </si>
+  <si>
+    <t>fK4ZXFr99U5</t>
+  </si>
+  <si>
+    <t>dLA0gL3Ul1z</t>
+  </si>
+  <si>
+    <t>UJ1fOQmk5kg</t>
+  </si>
+  <si>
+    <t>wzkboqfTTSl</t>
+  </si>
+  <si>
+    <t>L8CwMKeXVHD</t>
+  </si>
+  <si>
+    <t>stZ4OxwDrPf</t>
+  </si>
+  <si>
+    <t>GJM5lSbczra</t>
+  </si>
+  <si>
+    <t>X1CqeMieirL</t>
+  </si>
+  <si>
+    <t>IJUJDLnqRah</t>
+  </si>
+  <si>
+    <t>AIMRmvguXm4</t>
+  </si>
+  <si>
+    <t>c6545nEyuJc</t>
+  </si>
+  <si>
+    <t>dwbZZKs4vSN</t>
+  </si>
+  <si>
+    <t>jLtJvR1zHTa</t>
+  </si>
+  <si>
+    <t>GdNrQTzyVBc</t>
+  </si>
+  <si>
+    <t>KUhBOVo46Dq</t>
+  </si>
+  <si>
+    <t>YRiKxQn5hH3</t>
+  </si>
+  <si>
+    <t>M6z0DzSvVA3</t>
+  </si>
+  <si>
+    <t>bZw5dqyZ2sD</t>
+  </si>
+  <si>
+    <t>quXLRRIvBmR</t>
+  </si>
+  <si>
+    <t>o1UELDwNfg5</t>
+  </si>
+  <si>
+    <t>eHBBEXCQKZi</t>
+  </si>
+  <si>
+    <t>mhpG1RRiD2j</t>
+  </si>
+  <si>
+    <t>S2ChKNd1xCU</t>
+  </si>
+  <si>
+    <t>IYipa4VzUeO</t>
+  </si>
+  <si>
+    <t>cPqyJAF0vqR</t>
+  </si>
+  <si>
+    <t>tyxKHqkwh3m</t>
+  </si>
+  <si>
+    <t>T9uyBC7ihKI</t>
+  </si>
+  <si>
+    <t>aHCPQlKO5Oj</t>
+  </si>
+  <si>
+    <t>BATvaCTx4jD</t>
+  </si>
+  <si>
+    <t>zKb3GJOykeW</t>
+  </si>
+  <si>
+    <t>Yf9UMCBaJkf</t>
+  </si>
+  <si>
+    <t>U8hO1501lAn</t>
+  </si>
+  <si>
+    <t>hTRAWIOK1bo</t>
+  </si>
+  <si>
+    <t>wkmAexnoRIR</t>
+  </si>
+  <si>
+    <t>KSUQD1TP1qC</t>
+  </si>
+  <si>
+    <t>wKnJrGNV8LB</t>
+  </si>
+  <si>
+    <t>yV7I9ogEA23</t>
+  </si>
+  <si>
+    <t>K76zjUfHKgB</t>
+  </si>
+  <si>
+    <t>bBz0G88QjO2</t>
+  </si>
+  <si>
+    <t>XJnIUYMOjyo</t>
+  </si>
+  <si>
+    <t>StRZYAdwziN</t>
+  </si>
+  <si>
+    <t>qnopFXHt6gM</t>
+  </si>
+  <si>
+    <t>PqoXKltUTMG</t>
+  </si>
+  <si>
+    <t>fd7NwGcgxdi</t>
+  </si>
+  <si>
+    <t>e9PFC2SiTmm</t>
+  </si>
+  <si>
+    <t>ukZus2kTdWF</t>
+  </si>
+  <si>
+    <t>r1M0XKGrtVp</t>
+  </si>
+  <si>
+    <t>oRjB08eaOGi</t>
+  </si>
+  <si>
+    <t>UTLEJJh3B0n</t>
+  </si>
+  <si>
+    <t>PawHLqSLM4R</t>
+  </si>
+  <si>
+    <t>cPlhHTjhnQZ</t>
+  </si>
+  <si>
+    <t>jTuNW8q7rex</t>
+  </si>
+  <si>
+    <t>T1eyWTYvRAs</t>
+  </si>
+  <si>
+    <t>lSALobUWfKp</t>
+  </si>
+  <si>
+    <t>o05QzwP4giU</t>
+  </si>
+  <si>
+    <t>yZYk2nJutLz</t>
+  </si>
+  <si>
+    <t>E47jlXAGcz0</t>
+  </si>
+  <si>
+    <t>uFmnl64rj2z</t>
+  </si>
+  <si>
+    <t>TRU8mKzSqdf</t>
+  </si>
+  <si>
+    <t>NLTQvh7AMVk</t>
+  </si>
+  <si>
+    <t>GDybQxCXvej</t>
+  </si>
+  <si>
+    <t>B2DnM1v6av2</t>
+  </si>
+  <si>
+    <t>QRIZmaali3d</t>
+  </si>
+  <si>
+    <t>ABZRENkI0uM</t>
+  </si>
+  <si>
+    <t>WOJgE2umPQ7</t>
+  </si>
+  <si>
+    <t>PiC34foZyBx</t>
+  </si>
+  <si>
+    <t>KGHUSYGVNwx</t>
+  </si>
+  <si>
+    <t>NUw98cPXdPJ</t>
+  </si>
+  <si>
+    <t>x3OESzXeuCI</t>
+  </si>
+  <si>
+    <t>XNzAKJNPPgE</t>
+  </si>
+  <si>
+    <t>f3HYtYaKGBR</t>
+  </si>
+  <si>
+    <t>Pex2n6TpKsJ</t>
+  </si>
+  <si>
+    <t>nmdtN6rNgUg</t>
+  </si>
+  <si>
+    <t>rU6j5mu6zFN</t>
+  </si>
+  <si>
+    <t>sqa43dxdhEe</t>
+  </si>
+  <si>
+    <t>iDHT09pZD6Q</t>
+  </si>
+  <si>
+    <t>bt7MhupYFYE</t>
+  </si>
+  <si>
+    <t>MZtxXp6RVjM</t>
+  </si>
+  <si>
+    <t>cHdp0z7CTo7</t>
+  </si>
+  <si>
+    <t>IV6f0puYAjr</t>
+  </si>
+  <si>
+    <t>E6xNxQQ6OTF</t>
+  </si>
+  <si>
+    <t>ky6PCqQjSAw</t>
+  </si>
+  <si>
+    <t>zX6UYJlecgQ</t>
+  </si>
+  <si>
+    <t>BK57aiC4uvJ</t>
+  </si>
+  <si>
+    <t>EGi8oiE5Abe</t>
+  </si>
+  <si>
+    <t>YpTGTulEtgU</t>
+  </si>
+  <si>
+    <t>hXdJUsuuwLE</t>
+  </si>
+  <si>
+    <t>Hy3pdA7G2CC</t>
+  </si>
+  <si>
+    <t>QiAYVlHhBq1</t>
+  </si>
+  <si>
+    <t>xloNwiagAWh</t>
+  </si>
+  <si>
+    <t>d91qzmL3HJA</t>
+  </si>
+  <si>
+    <t>Eg14CJIrdBC</t>
+  </si>
+  <si>
+    <t>FUXl6IBXSHP</t>
+  </si>
+  <si>
+    <t>oeVuoGF7qBl</t>
+  </si>
+  <si>
+    <t>D57pR0OKqMH</t>
+  </si>
+  <si>
+    <t>DKteO6FDzOH</t>
+  </si>
+  <si>
+    <t>cCNCdwGepFF</t>
+  </si>
+  <si>
+    <t>JzDvH0V790n</t>
+  </si>
+  <si>
+    <t>lT74UQ2vWY2</t>
+  </si>
+  <si>
+    <t>U0rY8m7KADV</t>
+  </si>
+  <si>
+    <t>tTr7LKJKusR</t>
+  </si>
+  <si>
+    <t>KH62ia35VIZ</t>
+  </si>
+  <si>
+    <t>SsiA47as5VL</t>
+  </si>
+  <si>
+    <t>DKiCrjioOs1</t>
+  </si>
+  <si>
+    <t>noUT1q85Wu1</t>
+  </si>
+  <si>
+    <t>w2h1g3iYees</t>
+  </si>
+  <si>
+    <t>Fwt8OyNqzzl</t>
+  </si>
+  <si>
+    <t>VgGvzAQXCiC</t>
+  </si>
+  <si>
+    <t>ci1fnMwcRDJ</t>
+  </si>
+  <si>
+    <t>Z7oN4HcKjyt</t>
+  </si>
+  <si>
+    <t>VY1Nn2IttMp</t>
+  </si>
+  <si>
+    <t>VXGZDDOdnuw</t>
+  </si>
+  <si>
+    <t>x3NItY5VEjt</t>
+  </si>
+  <si>
+    <t>pNQCq6d7sz0</t>
+  </si>
+  <si>
+    <t>iypUX4a9NwB</t>
+  </si>
+  <si>
+    <t>VMM7CYoBk23</t>
+  </si>
+  <si>
+    <t>Sau34QPlU24</t>
+  </si>
+  <si>
+    <t>CdIIArqBnp6</t>
+  </si>
+  <si>
+    <t>DXBRwfFCvqm</t>
+  </si>
+  <si>
+    <t>pKikDWEhjqo</t>
+  </si>
+  <si>
+    <t>itmXuX0hMn2</t>
+  </si>
+  <si>
+    <t>DzthA2PaUm6</t>
+  </si>
+  <si>
+    <t>WNOHdQGvqiu</t>
+  </si>
+  <si>
+    <t>uF42TqPvRCL</t>
+  </si>
+  <si>
+    <t>iOKF7J8fFCT</t>
+  </si>
+  <si>
+    <t>Rr36LVZsAAr</t>
+  </si>
+  <si>
+    <t>CUNG0Cb510r</t>
+  </si>
+  <si>
+    <t>VuYBJFXIhdg</t>
+  </si>
+  <si>
+    <t>WDyVSonzM7m</t>
+  </si>
+  <si>
+    <t>WOZuVZXb6sJ</t>
+  </si>
+  <si>
+    <t>XKfFtdtoQ77</t>
+  </si>
+  <si>
+    <t>kiEIzpdT3zj</t>
+  </si>
+  <si>
+    <t>iM93omw9dQP</t>
+  </si>
+  <si>
+    <t>mEyDIQ1iTuu</t>
+  </si>
+  <si>
+    <t>Wd9cC6fr58o</t>
+  </si>
+  <si>
+    <t>mwTFruhaIu9</t>
+  </si>
+  <si>
+    <t>kqJuflINc5q</t>
+  </si>
+  <si>
+    <t>B2RQo8cWZ1Y</t>
+  </si>
+  <si>
+    <t>D9YrZO6KJlv</t>
+  </si>
+  <si>
+    <t>Fob12FaXk48</t>
+  </si>
+  <si>
+    <t>YkNAhawafkm</t>
+  </si>
+  <si>
+    <t>UP7AZcPq5Ia</t>
+  </si>
+  <si>
+    <t>N7YsETVV53K</t>
+  </si>
+  <si>
+    <t>eed9Gv8KAEA</t>
+  </si>
+  <si>
+    <t>GFaiR6mF38L</t>
+  </si>
+  <si>
+    <t>ynnWrjTYlvo</t>
+  </si>
+  <si>
+    <t>eNWFA60F4lb</t>
+  </si>
+  <si>
+    <t>q960MGMffwp</t>
+  </si>
+  <si>
+    <t>SeQrDnpQqUk</t>
+  </si>
+  <si>
+    <t>SY1df6lhPcE</t>
+  </si>
+  <si>
+    <t>AtqoUaXSoZD</t>
+  </si>
+  <si>
+    <t>BtaciOEh9xU</t>
+  </si>
+  <si>
+    <t>z2wtCwiE7nk</t>
+  </si>
+  <si>
+    <t>XpNLZevVGCZ</t>
+  </si>
+  <si>
+    <t>WrQfEFixsrj</t>
+  </si>
+  <si>
+    <t>tFVLcvoD16q</t>
+  </si>
+  <si>
+    <t>nX561wfqV5q</t>
+  </si>
+  <si>
+    <t>iRkTlIe86I2</t>
+  </si>
+  <si>
+    <t>D3Z0vxojFJn</t>
+  </si>
+  <si>
+    <t>doDFGxQGGxp</t>
+  </si>
+  <si>
+    <t>z7Q1IQ4vXnj</t>
+  </si>
+  <si>
+    <t>rlCCRB3RBac</t>
+  </si>
+  <si>
+    <t>iE0qmbYpSLS</t>
+  </si>
+  <si>
+    <t>triqdGsDtlU</t>
+  </si>
+  <si>
+    <t>Qw24EMlo7KH</t>
+  </si>
+  <si>
+    <t>jG5qLCUfmVb</t>
+  </si>
+  <si>
+    <t>nSbOMvzPtUd</t>
+  </si>
+  <si>
+    <t>hmtCYyh5laq</t>
+  </si>
+  <si>
+    <t>vB2Ia6AbWBc</t>
+  </si>
+  <si>
+    <t>qPu0mG5yPEh</t>
+  </si>
+  <si>
+    <t>KyFGwaognHn</t>
+  </si>
+  <si>
+    <t>Fy7BJ1h6Nfz</t>
+  </si>
+  <si>
+    <t>tHiHPOP2DcP</t>
+  </si>
+  <si>
+    <t>wjztOGWudzK</t>
+  </si>
+  <si>
+    <t>kfAKS77pXIY</t>
+  </si>
+  <si>
+    <t>z8FoWC4r8rv</t>
+  </si>
+  <si>
+    <t>cj10fc15uTd</t>
+  </si>
+  <si>
+    <t>sUNsjqu9MIX</t>
+  </si>
+  <si>
+    <t>CvtwpVIocpe</t>
+  </si>
+  <si>
+    <t>rA4P5U1vrGk</t>
+  </si>
+  <si>
+    <t>wHC9OxSU6I1</t>
+  </si>
+  <si>
+    <t>huKzYnrd0Zh</t>
+  </si>
+  <si>
+    <t>S52R0iNDBDL</t>
+  </si>
+  <si>
+    <t>HYLuELCmaVQ</t>
+  </si>
+  <si>
+    <t>xCo4BzpEmzG</t>
+  </si>
+  <si>
+    <t>Po4KdYmq6ST</t>
+  </si>
+  <si>
+    <t>UqmgTtCVdNz</t>
+  </si>
+  <si>
+    <t>QMyP9MoBwRp</t>
+  </si>
+  <si>
+    <t>QAL39BDKkZk</t>
+  </si>
+  <si>
+    <t>ja4QeEWZ3Qb</t>
+  </si>
+  <si>
+    <t>dHI119q0PPB</t>
+  </si>
+  <si>
+    <t>v9skpSOD9Cb</t>
+  </si>
+  <si>
+    <t>fY9uOLW3ME7</t>
+  </si>
+  <si>
+    <t>xvBYidT3iH0</t>
+  </si>
+  <si>
+    <t>H2vXFhLzom5</t>
+  </si>
+  <si>
+    <t>tEKZZ6T98v1</t>
+  </si>
+  <si>
+    <t>htKp6IOetp6</t>
+  </si>
+  <si>
+    <t>AndtRCDbz2A</t>
   </si>
 </sst>
 </file>
@@ -2702,16 +4772,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3A076C-ECA7-4854-BDDC-C813E3A40233}">
-  <dimension ref="A1:D372"/>
+  <dimension ref="A1:F372"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2724,8 +4796,14 @@
       <c r="D1" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>764</v>
+      </c>
+      <c r="F1" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2738,8 +4816,14 @@
       <c r="D2" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>766</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2752,8 +4836,14 @@
       <c r="D3" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>767</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -2766,8 +4856,14 @@
       <c r="D4" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>768</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -2780,8 +4876,14 @@
       <c r="D5" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>769</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -2794,8 +4896,14 @@
       <c r="D6" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>770</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -2808,8 +4916,14 @@
       <c r="D7" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>771</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -2822,8 +4936,14 @@
       <c r="D8" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>772</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -2836,8 +4956,14 @@
       <c r="D9" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>773</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -2850,8 +4976,11 @@
       <c r="D10" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -2864,8 +4993,14 @@
       <c r="D11" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>774</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -2878,8 +5013,14 @@
       <c r="D12" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>775</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -2892,8 +5033,14 @@
       <c r="D13" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -2906,8 +5053,14 @@
       <c r="D14" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>776</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -2920,8 +5073,14 @@
       <c r="D15" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>777</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -2934,8 +5093,14 @@
       <c r="D16" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>778</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -2948,8 +5113,14 @@
       <c r="D17" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>779</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2962,8 +5133,14 @@
       <c r="D18" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>780</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -2976,8 +5153,14 @@
       <c r="D19" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -2990,8 +5173,14 @@
       <c r="D20" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>781</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -3004,8 +5193,14 @@
       <c r="D21" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>782</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -3018,8 +5213,14 @@
       <c r="D22" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>783</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -3032,8 +5233,14 @@
       <c r="D23" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>784</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -3046,8 +5253,14 @@
       <c r="D24" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>785</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -3060,8 +5273,14 @@
       <c r="D25" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>786</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -3074,8 +5293,14 @@
       <c r="D26" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>787</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -3088,8 +5313,14 @@
       <c r="D27" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" t="s">
+        <v>788</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -3102,8 +5333,14 @@
       <c r="D28" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" t="s">
+        <v>789</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -3116,8 +5353,14 @@
       <c r="D29" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" t="s">
+        <v>790</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -3130,8 +5373,14 @@
       <c r="D30" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" t="s">
+        <v>791</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -3144,8 +5393,14 @@
       <c r="D31" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" t="s">
+        <v>792</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -3158,8 +5413,14 @@
       <c r="D32" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
+        <v>793</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -3172,8 +5433,14 @@
       <c r="D33" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>794</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -3186,8 +5453,14 @@
       <c r="D34" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>795</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -3200,8 +5473,11 @@
       <c r="D35" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -3214,8 +5490,14 @@
       <c r="D36" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>796</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -3228,8 +5510,14 @@
       <c r="D37" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
+        <v>797</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -3242,8 +5530,14 @@
       <c r="D38" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>798</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -3256,8 +5550,14 @@
       <c r="D39" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" t="s">
+        <v>799</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -3270,8 +5570,14 @@
       <c r="D40" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
+        <v>800</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -3284,8 +5590,14 @@
       <c r="D41" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41" t="s">
+        <v>801</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -3298,8 +5610,14 @@
       <c r="D42" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" t="s">
+        <v>802</v>
+      </c>
+      <c r="F42" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -3312,8 +5630,14 @@
       <c r="D43" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" t="s">
+        <v>803</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -3326,8 +5650,14 @@
       <c r="D44" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" t="s">
+        <v>804</v>
+      </c>
+      <c r="F44" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -3340,8 +5670,11 @@
       <c r="D45" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -3354,8 +5687,14 @@
       <c r="D46" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46" t="s">
+        <v>805</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -3368,8 +5707,14 @@
       <c r="D47" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" t="s">
+        <v>806</v>
+      </c>
+      <c r="F47" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -3382,8 +5727,14 @@
       <c r="D48" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" t="s">
+        <v>807</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -3396,8 +5747,11 @@
       <c r="D49" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -3410,8 +5764,14 @@
       <c r="D50" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" t="s">
+        <v>808</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -3424,8 +5784,14 @@
       <c r="D51" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" t="s">
+        <v>809</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>17</v>
       </c>
@@ -3438,8 +5804,14 @@
       <c r="D52" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" t="s">
+        <v>810</v>
+      </c>
+      <c r="F52" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>17</v>
       </c>
@@ -3452,8 +5824,14 @@
       <c r="D53" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" t="s">
+        <v>811</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -3466,8 +5844,14 @@
       <c r="D54" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" t="s">
+        <v>812</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -3480,8 +5864,14 @@
       <c r="D55" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E55" t="s">
+        <v>813</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -3494,8 +5884,14 @@
       <c r="D56" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E56" t="s">
+        <v>814</v>
+      </c>
+      <c r="F56" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -3508,8 +5904,14 @@
       <c r="D57" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E57" t="s">
+        <v>815</v>
+      </c>
+      <c r="F57" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -3522,8 +5924,14 @@
       <c r="D58" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" t="s">
+        <v>816</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -3536,8 +5944,14 @@
       <c r="D59" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E59" t="s">
+        <v>817</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -3550,8 +5964,14 @@
       <c r="D60" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" t="s">
+        <v>818</v>
+      </c>
+      <c r="F60" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -3564,8 +5984,14 @@
       <c r="D61" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E61" t="s">
+        <v>819</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>2</v>
       </c>
@@ -3578,8 +6004,14 @@
       <c r="D62" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E62" t="s">
+        <v>820</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>2</v>
       </c>
@@ -3592,8 +6024,14 @@
       <c r="D63" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E63" t="s">
+        <v>821</v>
+      </c>
+      <c r="F63" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>2</v>
       </c>
@@ -3606,8 +6044,14 @@
       <c r="D64" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E64" t="s">
+        <v>822</v>
+      </c>
+      <c r="F64" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -3620,8 +6064,14 @@
       <c r="D65" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E65" t="s">
+        <v>823</v>
+      </c>
+      <c r="F65" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -3634,8 +6084,14 @@
       <c r="D66" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E66" t="s">
+        <v>824</v>
+      </c>
+      <c r="F66" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>2</v>
       </c>
@@ -3648,8 +6104,14 @@
       <c r="D67" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E67" t="s">
+        <v>825</v>
+      </c>
+      <c r="F67" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>2</v>
       </c>
@@ -3662,8 +6124,14 @@
       <c r="D68" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E68" t="s">
+        <v>826</v>
+      </c>
+      <c r="F68" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>2</v>
       </c>
@@ -3676,8 +6144,14 @@
       <c r="D69" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E69" t="s">
+        <v>827</v>
+      </c>
+      <c r="F69" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>2</v>
       </c>
@@ -3690,8 +6164,14 @@
       <c r="D70" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E70" t="s">
+        <v>828</v>
+      </c>
+      <c r="F70" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>2</v>
       </c>
@@ -3704,8 +6184,14 @@
       <c r="D71" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E71" t="s">
+        <v>829</v>
+      </c>
+      <c r="F71" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>2</v>
       </c>
@@ -3718,8 +6204,14 @@
       <c r="D72" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E72" t="s">
+        <v>830</v>
+      </c>
+      <c r="F72" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>2</v>
       </c>
@@ -3732,8 +6224,14 @@
       <c r="D73" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E73" t="s">
+        <v>831</v>
+      </c>
+      <c r="F73" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>2</v>
       </c>
@@ -3746,8 +6244,14 @@
       <c r="D74" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E74" t="s">
+        <v>832</v>
+      </c>
+      <c r="F74" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>2</v>
       </c>
@@ -3760,8 +6264,14 @@
       <c r="D75" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E75" t="s">
+        <v>833</v>
+      </c>
+      <c r="F75" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>2</v>
       </c>
@@ -3774,8 +6284,14 @@
       <c r="D76" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E76" t="s">
+        <v>834</v>
+      </c>
+      <c r="F76" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>2</v>
       </c>
@@ -3788,8 +6304,14 @@
       <c r="D77" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E77" t="s">
+        <v>835</v>
+      </c>
+      <c r="F77" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>2</v>
       </c>
@@ -3802,8 +6324,14 @@
       <c r="D78" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E78" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F78" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>52</v>
       </c>
@@ -3816,8 +6344,14 @@
       <c r="D79" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E79" t="s">
+        <v>836</v>
+      </c>
+      <c r="F79" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>52</v>
       </c>
@@ -3830,8 +6364,14 @@
       <c r="D80" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" t="s">
+        <v>837</v>
+      </c>
+      <c r="F80" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>52</v>
       </c>
@@ -3844,8 +6384,14 @@
       <c r="D81" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E81" t="s">
+        <v>838</v>
+      </c>
+      <c r="F81" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>52</v>
       </c>
@@ -3858,8 +6404,14 @@
       <c r="D82" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E82" t="s">
+        <v>839</v>
+      </c>
+      <c r="F82" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>52</v>
       </c>
@@ -3872,8 +6424,11 @@
       <c r="D83" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E83" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>52</v>
       </c>
@@ -3886,8 +6441,14 @@
       <c r="D84" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E84" t="s">
+        <v>840</v>
+      </c>
+      <c r="F84" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>52</v>
       </c>
@@ -3900,8 +6461,14 @@
       <c r="D85" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E85" t="s">
+        <v>841</v>
+      </c>
+      <c r="F85" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>52</v>
       </c>
@@ -3914,8 +6481,14 @@
       <c r="D86" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E86" t="s">
+        <v>842</v>
+      </c>
+      <c r="F86" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>52</v>
       </c>
@@ -3928,8 +6501,14 @@
       <c r="D87" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E87" t="s">
+        <v>843</v>
+      </c>
+      <c r="F87" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>52</v>
       </c>
@@ -3942,8 +6521,14 @@
       <c r="D88" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E88" t="s">
+        <v>844</v>
+      </c>
+      <c r="F88" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>52</v>
       </c>
@@ -3956,8 +6541,14 @@
       <c r="D89" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E89" t="s">
+        <v>845</v>
+      </c>
+      <c r="F89" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>52</v>
       </c>
@@ -3970,8 +6561,14 @@
       <c r="D90" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E90" t="s">
+        <v>846</v>
+      </c>
+      <c r="F90" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>52</v>
       </c>
@@ -3984,8 +6581,14 @@
       <c r="D91" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E91" t="s">
+        <v>847</v>
+      </c>
+      <c r="F91" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>52</v>
       </c>
@@ -3998,8 +6601,14 @@
       <c r="D92" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E92" t="s">
+        <v>848</v>
+      </c>
+      <c r="F92" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>52</v>
       </c>
@@ -4012,8 +6621,14 @@
       <c r="D93" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E93" t="s">
+        <v>849</v>
+      </c>
+      <c r="F93" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>52</v>
       </c>
@@ -4026,8 +6641,14 @@
       <c r="D94" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E94" t="s">
+        <v>850</v>
+      </c>
+      <c r="F94" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>52</v>
       </c>
@@ -4040,8 +6661,14 @@
       <c r="D95" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E95" t="s">
+        <v>851</v>
+      </c>
+      <c r="F95" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>52</v>
       </c>
@@ -4054,8 +6681,14 @@
       <c r="D96" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E96" t="s">
+        <v>852</v>
+      </c>
+      <c r="F96" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>52</v>
       </c>
@@ -4068,8 +6701,14 @@
       <c r="D97" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E97" t="s">
+        <v>853</v>
+      </c>
+      <c r="F97" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>52</v>
       </c>
@@ -4082,8 +6721,14 @@
       <c r="D98" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E98" t="s">
+        <v>854</v>
+      </c>
+      <c r="F98" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>52</v>
       </c>
@@ -4096,8 +6741,14 @@
       <c r="D99" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E99" t="s">
+        <v>855</v>
+      </c>
+      <c r="F99" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>52</v>
       </c>
@@ -4110,8 +6761,14 @@
       <c r="D100" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E100" t="s">
+        <v>856</v>
+      </c>
+      <c r="F100" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>52</v>
       </c>
@@ -4124,8 +6781,11 @@
       <c r="D101" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E101" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>52</v>
       </c>
@@ -4138,8 +6798,11 @@
       <c r="D102" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E102" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>52</v>
       </c>
@@ -4152,8 +6815,11 @@
       <c r="D103" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E103" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>52</v>
       </c>
@@ -4166,8 +6832,14 @@
       <c r="D104" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E104" t="s">
+        <v>857</v>
+      </c>
+      <c r="F104" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>52</v>
       </c>
@@ -4180,8 +6852,14 @@
       <c r="D105" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E105" t="s">
+        <v>858</v>
+      </c>
+      <c r="F105" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>52</v>
       </c>
@@ -4194,8 +6872,14 @@
       <c r="D106" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E106" t="s">
+        <v>859</v>
+      </c>
+      <c r="F106" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>52</v>
       </c>
@@ -4208,8 +6892,14 @@
       <c r="D107" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E107" t="s">
+        <v>860</v>
+      </c>
+      <c r="F107" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>52</v>
       </c>
@@ -4222,8 +6912,14 @@
       <c r="D108" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E108" t="s">
+        <v>861</v>
+      </c>
+      <c r="F108" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>52</v>
       </c>
@@ -4236,8 +6932,14 @@
       <c r="D109" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E109" t="s">
+        <v>862</v>
+      </c>
+      <c r="F109" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>52</v>
       </c>
@@ -4250,8 +6952,14 @@
       <c r="D110" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E110" t="s">
+        <v>863</v>
+      </c>
+      <c r="F110" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>52</v>
       </c>
@@ -4264,8 +6972,14 @@
       <c r="D111" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E111" t="s">
+        <v>864</v>
+      </c>
+      <c r="F111" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>52</v>
       </c>
@@ -4278,8 +6992,11 @@
       <c r="D112" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E112" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>52</v>
       </c>
@@ -4292,8 +7009,11 @@
       <c r="D113" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E113" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>52</v>
       </c>
@@ -4306,8 +7026,14 @@
       <c r="D114" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E114" t="s">
+        <v>865</v>
+      </c>
+      <c r="F114" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>52</v>
       </c>
@@ -4320,8 +7046,14 @@
       <c r="D115" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E115" t="s">
+        <v>866</v>
+      </c>
+      <c r="F115" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>52</v>
       </c>
@@ -4334,8 +7066,11 @@
       <c r="D116" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E116" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>52</v>
       </c>
@@ -4348,8 +7083,11 @@
       <c r="D117" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E117" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>52</v>
       </c>
@@ -4362,8 +7100,14 @@
       <c r="D118" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E118" t="s">
+        <v>867</v>
+      </c>
+      <c r="F118" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>52</v>
       </c>
@@ -4376,8 +7120,11 @@
       <c r="D119" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E119" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>52</v>
       </c>
@@ -4390,8 +7137,11 @@
       <c r="D120" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E120" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>52</v>
       </c>
@@ -4404,8 +7154,14 @@
       <c r="D121" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E121" t="s">
+        <v>868</v>
+      </c>
+      <c r="F121" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>52</v>
       </c>
@@ -4418,8 +7174,14 @@
       <c r="D122" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E122" t="s">
+        <v>869</v>
+      </c>
+      <c r="F122" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>52</v>
       </c>
@@ -4432,8 +7194,14 @@
       <c r="D123" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E123" t="s">
+        <v>870</v>
+      </c>
+      <c r="F123" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>52</v>
       </c>
@@ -4446,8 +7214,14 @@
       <c r="D124" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E124" t="s">
+        <v>871</v>
+      </c>
+      <c r="F124" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>52</v>
       </c>
@@ -4460,8 +7234,11 @@
       <c r="D125" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E125" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>52</v>
       </c>
@@ -4474,8 +7251,14 @@
       <c r="D126" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E126" t="s">
+        <v>872</v>
+      </c>
+      <c r="F126" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>17</v>
       </c>
@@ -4488,8 +7271,14 @@
       <c r="D127" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E127" t="s">
+        <v>873</v>
+      </c>
+      <c r="F127" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>17</v>
       </c>
@@ -4502,8 +7291,14 @@
       <c r="D128" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E128" t="s">
+        <v>874</v>
+      </c>
+      <c r="F128" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>17</v>
       </c>
@@ -4516,8 +7311,14 @@
       <c r="D129" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E129" t="s">
+        <v>875</v>
+      </c>
+      <c r="F129" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>17</v>
       </c>
@@ -4527,8 +7328,14 @@
       <c r="C130" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E130" t="s">
+        <v>876</v>
+      </c>
+      <c r="F130" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>17</v>
       </c>
@@ -4541,8 +7348,14 @@
       <c r="D131" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E131" t="s">
+        <v>877</v>
+      </c>
+      <c r="F131" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>17</v>
       </c>
@@ -4555,8 +7368,14 @@
       <c r="D132" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E132" t="s">
+        <v>878</v>
+      </c>
+      <c r="F132" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>17</v>
       </c>
@@ -4569,8 +7388,14 @@
       <c r="D133" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E133" t="s">
+        <v>879</v>
+      </c>
+      <c r="F133" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>17</v>
       </c>
@@ -4583,8 +7408,14 @@
       <c r="D134" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E134" t="s">
+        <v>880</v>
+      </c>
+      <c r="F134" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>17</v>
       </c>
@@ -4597,8 +7428,14 @@
       <c r="D135" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E135" t="s">
+        <v>881</v>
+      </c>
+      <c r="F135" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>17</v>
       </c>
@@ -4611,8 +7448,14 @@
       <c r="D136" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E136" t="s">
+        <v>882</v>
+      </c>
+      <c r="F136" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>17</v>
       </c>
@@ -4625,8 +7468,14 @@
       <c r="D137" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E137" t="s">
+        <v>883</v>
+      </c>
+      <c r="F137" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>17</v>
       </c>
@@ -4639,8 +7488,14 @@
       <c r="D138" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E138" t="s">
+        <v>884</v>
+      </c>
+      <c r="F138" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>17</v>
       </c>
@@ -4653,8 +7508,14 @@
       <c r="D139" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E139" t="s">
+        <v>885</v>
+      </c>
+      <c r="F139" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>17</v>
       </c>
@@ -4667,8 +7528,14 @@
       <c r="D140" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E140" t="s">
+        <v>886</v>
+      </c>
+      <c r="F140" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>52</v>
       </c>
@@ -4681,8 +7548,14 @@
       <c r="D141" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E141" t="s">
+        <v>887</v>
+      </c>
+      <c r="F141" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>52</v>
       </c>
@@ -4695,8 +7568,14 @@
       <c r="D142" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E142" t="s">
+        <v>888</v>
+      </c>
+      <c r="F142" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>52</v>
       </c>
@@ -4709,8 +7588,14 @@
       <c r="D143" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E143" t="s">
+        <v>889</v>
+      </c>
+      <c r="F143" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>52</v>
       </c>
@@ -4723,8 +7608,14 @@
       <c r="D144" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E144" t="s">
+        <v>890</v>
+      </c>
+      <c r="F144" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>52</v>
       </c>
@@ -4737,8 +7628,11 @@
       <c r="D145" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E145" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>52</v>
       </c>
@@ -4751,8 +7645,14 @@
       <c r="D146" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E146" t="s">
+        <v>891</v>
+      </c>
+      <c r="F146" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>52</v>
       </c>
@@ -4765,8 +7665,14 @@
       <c r="D147" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E147" t="s">
+        <v>892</v>
+      </c>
+      <c r="F147" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>52</v>
       </c>
@@ -4779,8 +7685,14 @@
       <c r="D148" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E148" t="s">
+        <v>893</v>
+      </c>
+      <c r="F148" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>52</v>
       </c>
@@ -4793,8 +7705,14 @@
       <c r="D149" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E149" t="s">
+        <v>894</v>
+      </c>
+      <c r="F149" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>52</v>
       </c>
@@ -4807,8 +7725,14 @@
       <c r="D150" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E150" t="s">
+        <v>895</v>
+      </c>
+      <c r="F150" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>52</v>
       </c>
@@ -4821,8 +7745,14 @@
       <c r="D151" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E151" t="s">
+        <v>896</v>
+      </c>
+      <c r="F151" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>52</v>
       </c>
@@ -4835,8 +7765,14 @@
       <c r="D152" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E152" t="s">
+        <v>897</v>
+      </c>
+      <c r="F152" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>52</v>
       </c>
@@ -4849,8 +7785,14 @@
       <c r="D153" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E153" t="s">
+        <v>898</v>
+      </c>
+      <c r="F153" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>52</v>
       </c>
@@ -4863,8 +7805,14 @@
       <c r="D154" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E154" t="s">
+        <v>899</v>
+      </c>
+      <c r="F154" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>166</v>
       </c>
@@ -4877,8 +7825,14 @@
       <c r="D155" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E155" t="s">
+        <v>900</v>
+      </c>
+      <c r="F155" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>166</v>
       </c>
@@ -4891,8 +7845,14 @@
       <c r="D156" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E156" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F156" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>166</v>
       </c>
@@ -4905,8 +7865,11 @@
       <c r="D157" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F157" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>166</v>
       </c>
@@ -4919,8 +7882,11 @@
       <c r="D158" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E158" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>166</v>
       </c>
@@ -4933,8 +7899,14 @@
       <c r="D159" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E159" t="s">
+        <v>901</v>
+      </c>
+      <c r="F159" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>166</v>
       </c>
@@ -4947,8 +7919,14 @@
       <c r="D160" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E160" t="s">
+        <v>902</v>
+      </c>
+      <c r="F160" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>166</v>
       </c>
@@ -4961,8 +7939,11 @@
       <c r="D161" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E161" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>166</v>
       </c>
@@ -4975,8 +7956,14 @@
       <c r="D162" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E162" t="s">
+        <v>903</v>
+      </c>
+      <c r="F162" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>166</v>
       </c>
@@ -4989,8 +7976,14 @@
       <c r="D163" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E163" t="s">
+        <v>904</v>
+      </c>
+      <c r="F163" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>166</v>
       </c>
@@ -5003,8 +7996,14 @@
       <c r="D164" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E164" t="s">
+        <v>905</v>
+      </c>
+      <c r="F164" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>166</v>
       </c>
@@ -5017,8 +8016,14 @@
       <c r="D165" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E165" t="s">
+        <v>906</v>
+      </c>
+      <c r="F165" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>166</v>
       </c>
@@ -5031,8 +8036,14 @@
       <c r="D166" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E166" t="s">
+        <v>907</v>
+      </c>
+      <c r="F166" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>166</v>
       </c>
@@ -5045,8 +8056,14 @@
       <c r="D167" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E167" t="s">
+        <v>908</v>
+      </c>
+      <c r="F167" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>166</v>
       </c>
@@ -5059,8 +8076,14 @@
       <c r="D168" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E168" t="s">
+        <v>909</v>
+      </c>
+      <c r="F168" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>166</v>
       </c>
@@ -5073,8 +8096,14 @@
       <c r="D169" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E169" t="s">
+        <v>910</v>
+      </c>
+      <c r="F169" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>166</v>
       </c>
@@ -5087,8 +8116,14 @@
       <c r="D170" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E170" t="s">
+        <v>911</v>
+      </c>
+      <c r="F170" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>166</v>
       </c>
@@ -5101,8 +8136,14 @@
       <c r="D171" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E171" t="s">
+        <v>912</v>
+      </c>
+      <c r="F171" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>166</v>
       </c>
@@ -5115,8 +8156,14 @@
       <c r="D172" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E172" t="s">
+        <v>913</v>
+      </c>
+      <c r="F172" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>166</v>
       </c>
@@ -5129,8 +8176,14 @@
       <c r="D173" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E173" t="s">
+        <v>914</v>
+      </c>
+      <c r="F173" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>166</v>
       </c>
@@ -5143,8 +8196,14 @@
       <c r="D174" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E174" t="s">
+        <v>915</v>
+      </c>
+      <c r="F174" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>188</v>
       </c>
@@ -5157,8 +8216,14 @@
       <c r="D175" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E175" t="s">
+        <v>916</v>
+      </c>
+      <c r="F175" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>188</v>
       </c>
@@ -5171,8 +8236,14 @@
       <c r="D176" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E176" t="s">
+        <v>917</v>
+      </c>
+      <c r="F176" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>188</v>
       </c>
@@ -5185,8 +8256,14 @@
       <c r="D177" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E177" t="s">
+        <v>918</v>
+      </c>
+      <c r="F177" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>188</v>
       </c>
@@ -5199,8 +8276,14 @@
       <c r="D178" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E178" t="s">
+        <v>919</v>
+      </c>
+      <c r="F178" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>188</v>
       </c>
@@ -5213,8 +8296,14 @@
       <c r="D179" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E179" t="s">
+        <v>920</v>
+      </c>
+      <c r="F179" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>188</v>
       </c>
@@ -5227,8 +8316,14 @@
       <c r="D180" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E180" t="s">
+        <v>921</v>
+      </c>
+      <c r="F180" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>188</v>
       </c>
@@ -5241,8 +8336,14 @@
       <c r="D181" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E181" t="s">
+        <v>922</v>
+      </c>
+      <c r="F181" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>188</v>
       </c>
@@ -5255,8 +8356,14 @@
       <c r="D182" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E182" t="s">
+        <v>923</v>
+      </c>
+      <c r="F182" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>188</v>
       </c>
@@ -5269,8 +8376,14 @@
       <c r="D183" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E183" t="s">
+        <v>924</v>
+      </c>
+      <c r="F183" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>188</v>
       </c>
@@ -5283,8 +8396,14 @@
       <c r="D184" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E184" t="s">
+        <v>925</v>
+      </c>
+      <c r="F184" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>188</v>
       </c>
@@ -5297,8 +8416,14 @@
       <c r="D185" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E185" t="s">
+        <v>926</v>
+      </c>
+      <c r="F185" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>188</v>
       </c>
@@ -5311,8 +8436,14 @@
       <c r="D186" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E186" t="s">
+        <v>927</v>
+      </c>
+      <c r="F186" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>188</v>
       </c>
@@ -5325,8 +8456,14 @@
       <c r="D187" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E187" t="s">
+        <v>928</v>
+      </c>
+      <c r="F187" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>188</v>
       </c>
@@ -5339,8 +8476,14 @@
       <c r="D188" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E188" t="s">
+        <v>929</v>
+      </c>
+      <c r="F188" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>188</v>
       </c>
@@ -5353,8 +8496,14 @@
       <c r="D189" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E189" t="s">
+        <v>930</v>
+      </c>
+      <c r="F189" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>188</v>
       </c>
@@ -5367,8 +8516,14 @@
       <c r="D190" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E190" t="s">
+        <v>931</v>
+      </c>
+      <c r="F190" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>188</v>
       </c>
@@ -5381,8 +8536,14 @@
       <c r="D191" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E191" t="s">
+        <v>932</v>
+      </c>
+      <c r="F191" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>188</v>
       </c>
@@ -5395,8 +8556,14 @@
       <c r="D192" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E192" t="s">
+        <v>933</v>
+      </c>
+      <c r="F192" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>188</v>
       </c>
@@ -5409,8 +8576,14 @@
       <c r="D193" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E193" t="s">
+        <v>934</v>
+      </c>
+      <c r="F193" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>188</v>
       </c>
@@ -5423,8 +8596,14 @@
       <c r="D194" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E194" t="s">
+        <v>935</v>
+      </c>
+      <c r="F194" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>188</v>
       </c>
@@ -5437,8 +8616,14 @@
       <c r="D195" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E195" t="s">
+        <v>936</v>
+      </c>
+      <c r="F195" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>188</v>
       </c>
@@ -5451,8 +8636,14 @@
       <c r="D196" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E196" t="s">
+        <v>937</v>
+      </c>
+      <c r="F196" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>188</v>
       </c>
@@ -5465,8 +8656,14 @@
       <c r="D197" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E197" t="s">
+        <v>938</v>
+      </c>
+      <c r="F197" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>188</v>
       </c>
@@ -5479,8 +8676,14 @@
       <c r="D198" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E198" t="s">
+        <v>939</v>
+      </c>
+      <c r="F198" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>188</v>
       </c>
@@ -5493,8 +8696,14 @@
       <c r="D199" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E199" t="s">
+        <v>940</v>
+      </c>
+      <c r="F199" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>188</v>
       </c>
@@ -5507,8 +8716,14 @@
       <c r="D200" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E200" t="s">
+        <v>941</v>
+      </c>
+      <c r="F200" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>188</v>
       </c>
@@ -5521,8 +8736,14 @@
       <c r="D201" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E201" t="s">
+        <v>942</v>
+      </c>
+      <c r="F201" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>188</v>
       </c>
@@ -5535,8 +8756,14 @@
       <c r="D202" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E202" t="s">
+        <v>943</v>
+      </c>
+      <c r="F202" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>188</v>
       </c>
@@ -5549,8 +8776,14 @@
       <c r="D203" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E203" t="s">
+        <v>944</v>
+      </c>
+      <c r="F203" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>188</v>
       </c>
@@ -5563,8 +8796,14 @@
       <c r="D204" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E204" t="s">
+        <v>945</v>
+      </c>
+      <c r="F204" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>188</v>
       </c>
@@ -5577,8 +8816,14 @@
       <c r="D205" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E205" t="s">
+        <v>946</v>
+      </c>
+      <c r="F205" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>188</v>
       </c>
@@ -5591,8 +8836,14 @@
       <c r="D206" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E206" t="s">
+        <v>947</v>
+      </c>
+      <c r="F206" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>188</v>
       </c>
@@ -5605,8 +8856,14 @@
       <c r="D207" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E207" t="s">
+        <v>948</v>
+      </c>
+      <c r="F207" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>188</v>
       </c>
@@ -5619,8 +8876,14 @@
       <c r="D208" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E208" t="s">
+        <v>949</v>
+      </c>
+      <c r="F208" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>188</v>
       </c>
@@ -5633,8 +8896,14 @@
       <c r="D209" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E209" t="s">
+        <v>950</v>
+      </c>
+      <c r="F209" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>188</v>
       </c>
@@ -5647,8 +8916,14 @@
       <c r="D210" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E210" t="s">
+        <v>951</v>
+      </c>
+      <c r="F210" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>166</v>
       </c>
@@ -5661,8 +8936,14 @@
       <c r="D211" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E211" t="s">
+        <v>952</v>
+      </c>
+      <c r="F211" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>166</v>
       </c>
@@ -5675,8 +8956,14 @@
       <c r="D212" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E212" t="s">
+        <v>953</v>
+      </c>
+      <c r="F212" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>166</v>
       </c>
@@ -5689,8 +8976,14 @@
       <c r="D213" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E213" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F213" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>166</v>
       </c>
@@ -5703,8 +8996,14 @@
       <c r="D214" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E214" t="s">
+        <v>954</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>166</v>
       </c>
@@ -5717,8 +9016,14 @@
       <c r="D215" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E215" t="s">
+        <v>955</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>166</v>
       </c>
@@ -5731,8 +9036,14 @@
       <c r="D216" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E216" t="s">
+        <v>956</v>
+      </c>
+      <c r="F216" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>166</v>
       </c>
@@ -5745,8 +9056,14 @@
       <c r="D217" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E217" t="s">
+        <v>957</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>166</v>
       </c>
@@ -5759,8 +9076,14 @@
       <c r="D218" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E218" t="s">
+        <v>958</v>
+      </c>
+      <c r="F218" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>166</v>
       </c>
@@ -5773,8 +9096,14 @@
       <c r="D219" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E219" t="s">
+        <v>959</v>
+      </c>
+      <c r="F219" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>166</v>
       </c>
@@ -5787,8 +9116,14 @@
       <c r="D220" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E220" t="s">
+        <v>960</v>
+      </c>
+      <c r="F220" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>166</v>
       </c>
@@ -5801,8 +9136,14 @@
       <c r="D221" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E221" t="s">
+        <v>961</v>
+      </c>
+      <c r="F221" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>52</v>
       </c>
@@ -5815,8 +9156,14 @@
       <c r="D222" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E222" t="s">
+        <v>962</v>
+      </c>
+      <c r="F222" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>52</v>
       </c>
@@ -5829,8 +9176,14 @@
       <c r="D223" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E223" t="s">
+        <v>963</v>
+      </c>
+      <c r="F223" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>52</v>
       </c>
@@ -5843,8 +9196,14 @@
       <c r="D224" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E224" t="s">
+        <v>964</v>
+      </c>
+      <c r="F224" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>52</v>
       </c>
@@ -5857,8 +9216,14 @@
       <c r="D225" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E225" t="s">
+        <v>965</v>
+      </c>
+      <c r="F225" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>52</v>
       </c>
@@ -5871,8 +9236,14 @@
       <c r="D226" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E226" t="s">
+        <v>966</v>
+      </c>
+      <c r="F226" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>52</v>
       </c>
@@ -5885,8 +9256,11 @@
       <c r="D227" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E227" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>52</v>
       </c>
@@ -5899,8 +9273,14 @@
       <c r="D228" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E228" t="s">
+        <v>967</v>
+      </c>
+      <c r="F228" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>52</v>
       </c>
@@ -5913,8 +9293,14 @@
       <c r="D229" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E229" t="s">
+        <v>968</v>
+      </c>
+      <c r="F229" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>52</v>
       </c>
@@ -5927,8 +9313,14 @@
       <c r="D230" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E230" t="s">
+        <v>969</v>
+      </c>
+      <c r="F230" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>52</v>
       </c>
@@ -5941,8 +9333,14 @@
       <c r="D231" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E231" t="s">
+        <v>970</v>
+      </c>
+      <c r="F231" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>52</v>
       </c>
@@ -5955,8 +9353,11 @@
       <c r="D232" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E232" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>52</v>
       </c>
@@ -5969,8 +9370,14 @@
       <c r="D233" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E233" t="s">
+        <v>971</v>
+      </c>
+      <c r="F233" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>52</v>
       </c>
@@ -5983,8 +9390,14 @@
       <c r="D234" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E234" t="s">
+        <v>972</v>
+      </c>
+      <c r="F234" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>52</v>
       </c>
@@ -5997,8 +9410,14 @@
       <c r="D235" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E235" t="s">
+        <v>973</v>
+      </c>
+      <c r="F235" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>52</v>
       </c>
@@ -6011,8 +9430,11 @@
       <c r="D236" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E236" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>166</v>
       </c>
@@ -6025,8 +9447,14 @@
       <c r="D237" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E237" t="s">
+        <v>974</v>
+      </c>
+      <c r="F237" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>166</v>
       </c>
@@ -6039,8 +9467,14 @@
       <c r="D238" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E238" t="s">
+        <v>975</v>
+      </c>
+      <c r="F238" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>166</v>
       </c>
@@ -6053,8 +9487,14 @@
       <c r="D239" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E239" t="s">
+        <v>976</v>
+      </c>
+      <c r="F239" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>166</v>
       </c>
@@ -6067,8 +9507,14 @@
       <c r="D240" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E240" t="s">
+        <v>977</v>
+      </c>
+      <c r="F240" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>166</v>
       </c>
@@ -6081,8 +9527,14 @@
       <c r="D241" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E241" t="s">
+        <v>978</v>
+      </c>
+      <c r="F241" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>166</v>
       </c>
@@ -6095,8 +9547,14 @@
       <c r="D242" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E242" t="s">
+        <v>979</v>
+      </c>
+      <c r="F242" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>166</v>
       </c>
@@ -6109,8 +9567,14 @@
       <c r="D243" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E243" t="s">
+        <v>980</v>
+      </c>
+      <c r="F243" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>166</v>
       </c>
@@ -6123,8 +9587,14 @@
       <c r="D244" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E244" t="s">
+        <v>981</v>
+      </c>
+      <c r="F244" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>166</v>
       </c>
@@ -6137,8 +9607,14 @@
       <c r="D245" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E245" t="s">
+        <v>982</v>
+      </c>
+      <c r="F245" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>166</v>
       </c>
@@ -6151,8 +9627,14 @@
       <c r="D246" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E246" t="s">
+        <v>983</v>
+      </c>
+      <c r="F246" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>166</v>
       </c>
@@ -6165,8 +9647,14 @@
       <c r="D247" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E247" t="s">
+        <v>984</v>
+      </c>
+      <c r="F247" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>166</v>
       </c>
@@ -6179,8 +9667,14 @@
       <c r="D248" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E248" t="s">
+        <v>985</v>
+      </c>
+      <c r="F248" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>166</v>
       </c>
@@ -6193,8 +9687,14 @@
       <c r="D249" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E249" t="s">
+        <v>986</v>
+      </c>
+      <c r="F249" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>166</v>
       </c>
@@ -6207,8 +9707,11 @@
       <c r="D250" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E250" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>166</v>
       </c>
@@ -6221,8 +9724,14 @@
       <c r="D251" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E251" t="s">
+        <v>987</v>
+      </c>
+      <c r="F251" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>166</v>
       </c>
@@ -6235,8 +9744,14 @@
       <c r="D252" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E252" t="s">
+        <v>988</v>
+      </c>
+      <c r="F252" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>166</v>
       </c>
@@ -6249,8 +9764,14 @@
       <c r="D253" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E253" t="s">
+        <v>989</v>
+      </c>
+      <c r="F253" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>166</v>
       </c>
@@ -6263,8 +9784,14 @@
       <c r="D254" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E254" t="s">
+        <v>990</v>
+      </c>
+      <c r="F254" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>166</v>
       </c>
@@ -6277,8 +9804,14 @@
       <c r="D255" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E255" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F255" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>166</v>
       </c>
@@ -6291,8 +9824,11 @@
       <c r="D256" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E256" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>166</v>
       </c>
@@ -6305,8 +9841,14 @@
       <c r="D257" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E257" t="s">
+        <v>991</v>
+      </c>
+      <c r="F257" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>166</v>
       </c>
@@ -6319,8 +9861,14 @@
       <c r="D258" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E258" t="s">
+        <v>992</v>
+      </c>
+      <c r="F258" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>166</v>
       </c>
@@ -6333,8 +9881,14 @@
       <c r="D259" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E259" t="s">
+        <v>993</v>
+      </c>
+      <c r="F259" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>166</v>
       </c>
@@ -6347,8 +9901,14 @@
       <c r="D260" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E260" t="s">
+        <v>994</v>
+      </c>
+      <c r="F260" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>166</v>
       </c>
@@ -6361,8 +9921,14 @@
       <c r="D261" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E261" t="s">
+        <v>995</v>
+      </c>
+      <c r="F261" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>166</v>
       </c>
@@ -6375,8 +9941,14 @@
       <c r="D262" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E262" t="s">
+        <v>996</v>
+      </c>
+      <c r="F262" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>166</v>
       </c>
@@ -6389,8 +9961,14 @@
       <c r="D263" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E263" t="s">
+        <v>997</v>
+      </c>
+      <c r="F263" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>166</v>
       </c>
@@ -6403,8 +9981,14 @@
       <c r="D264" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E264" t="s">
+        <v>998</v>
+      </c>
+      <c r="F264" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>166</v>
       </c>
@@ -6417,8 +10001,14 @@
       <c r="D265" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E265" t="s">
+        <v>999</v>
+      </c>
+      <c r="F265" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>166</v>
       </c>
@@ -6431,8 +10021,11 @@
       <c r="D266" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E266" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>166</v>
       </c>
@@ -6445,8 +10038,14 @@
       <c r="D267" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E267" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F267" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>166</v>
       </c>
@@ -6459,8 +10058,14 @@
       <c r="D268" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E268" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F268" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>166</v>
       </c>
@@ -6473,8 +10078,14 @@
       <c r="D269" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E269" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F269" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>188</v>
       </c>
@@ -6487,8 +10098,11 @@
       <c r="D270" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E270" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>188</v>
       </c>
@@ -6501,8 +10115,11 @@
       <c r="D271" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E271" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>188</v>
       </c>
@@ -6515,8 +10132,14 @@
       <c r="D272" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E272" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F272" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>188</v>
       </c>
@@ -6529,8 +10152,11 @@
       <c r="D273" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E273" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>188</v>
       </c>
@@ -6543,8 +10169,14 @@
       <c r="D274" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E274" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F274" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>188</v>
       </c>
@@ -6557,8 +10189,11 @@
       <c r="D275" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E275" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>188</v>
       </c>
@@ -6571,8 +10206,14 @@
       <c r="D276" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E276" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F276" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>188</v>
       </c>
@@ -6585,8 +10226,14 @@
       <c r="D277" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E277" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F277" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>188</v>
       </c>
@@ -6599,8 +10246,11 @@
       <c r="D278" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E278" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>188</v>
       </c>
@@ -6613,8 +10263,14 @@
       <c r="D279" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E279" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F279" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>188</v>
       </c>
@@ -6627,8 +10283,14 @@
       <c r="D280" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E280" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F280" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>188</v>
       </c>
@@ -6641,8 +10303,14 @@
       <c r="D281" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E281" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F281" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>188</v>
       </c>
@@ -6655,8 +10323,14 @@
       <c r="D282" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E282" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F282" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>188</v>
       </c>
@@ -6669,8 +10343,11 @@
       <c r="D283" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E283" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>188</v>
       </c>
@@ -6683,8 +10360,14 @@
       <c r="D284" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E284" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F284" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>188</v>
       </c>
@@ -6697,8 +10380,14 @@
       <c r="D285" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E285" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F285" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>188</v>
       </c>
@@ -6711,8 +10400,11 @@
       <c r="D286" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E286" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>188</v>
       </c>
@@ -6725,8 +10417,14 @@
       <c r="D287" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E287" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F287" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>188</v>
       </c>
@@ -6739,8 +10437,14 @@
       <c r="D288" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E288" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F288" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>188</v>
       </c>
@@ -6753,8 +10457,14 @@
       <c r="D289" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E289" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F289" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>188</v>
       </c>
@@ -6767,8 +10477,11 @@
       <c r="D290" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E290" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>188</v>
       </c>
@@ -6781,8 +10494,14 @@
       <c r="D291" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E291" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F291" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>188</v>
       </c>
@@ -6795,8 +10514,11 @@
       <c r="D292" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E292" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>188</v>
       </c>
@@ -6809,8 +10531,14 @@
       <c r="D293" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E293" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F293" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>188</v>
       </c>
@@ -6823,8 +10551,11 @@
       <c r="D294" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E294" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>188</v>
       </c>
@@ -6837,8 +10568,14 @@
       <c r="D295" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E295" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F295" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>188</v>
       </c>
@@ -6851,8 +10588,14 @@
       <c r="D296" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E296" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F296" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>188</v>
       </c>
@@ -6865,8 +10608,11 @@
       <c r="D297" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F297" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>188</v>
       </c>
@@ -6879,8 +10625,11 @@
       <c r="D298" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E298" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>188</v>
       </c>
@@ -6893,8 +10642,14 @@
       <c r="D299" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E299" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F299" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>188</v>
       </c>
@@ -6907,8 +10662,14 @@
       <c r="D300" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E300" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F300" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>188</v>
       </c>
@@ -6921,8 +10682,14 @@
       <c r="D301" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E301" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F301" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>188</v>
       </c>
@@ -6935,8 +10702,14 @@
       <c r="D302" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E302" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F302" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>188</v>
       </c>
@@ -6949,8 +10722,14 @@
       <c r="D303" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E303" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F303" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>188</v>
       </c>
@@ -6963,8 +10742,14 @@
       <c r="D304" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E304" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F304" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>188</v>
       </c>
@@ -6977,8 +10762,14 @@
       <c r="D305" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E305" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F305" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>188</v>
       </c>
@@ -6991,8 +10782,14 @@
       <c r="D306" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E306" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F306" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>188</v>
       </c>
@@ -7005,8 +10802,14 @@
       <c r="D307" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E307" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F307" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>188</v>
       </c>
@@ -7019,8 +10822,11 @@
       <c r="D308" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E308" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>188</v>
       </c>
@@ -7033,8 +10839,14 @@
       <c r="D309" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E309" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F309" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>188</v>
       </c>
@@ -7047,8 +10859,14 @@
       <c r="D310" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E310" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F310" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>188</v>
       </c>
@@ -7061,8 +10879,14 @@
       <c r="D311" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E311" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F311" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>188</v>
       </c>
@@ -7075,8 +10899,14 @@
       <c r="D312" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E312" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F312" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>188</v>
       </c>
@@ -7089,8 +10919,14 @@
       <c r="D313" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E313" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F313" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>188</v>
       </c>
@@ -7103,8 +10939,14 @@
       <c r="D314" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E314" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F314" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>188</v>
       </c>
@@ -7117,8 +10959,14 @@
       <c r="D315" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E315" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F315" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>188</v>
       </c>
@@ -7131,8 +10979,14 @@
       <c r="D316" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E316" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F316" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>188</v>
       </c>
@@ -7145,8 +10999,14 @@
       <c r="D317" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E317" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F317" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>188</v>
       </c>
@@ -7159,8 +11019,14 @@
       <c r="D318" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E318" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F318" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>188</v>
       </c>
@@ -7173,8 +11039,14 @@
       <c r="D319" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E319" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F319" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>188</v>
       </c>
@@ -7187,8 +11059,14 @@
       <c r="D320" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E320" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F320" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>188</v>
       </c>
@@ -7201,8 +11079,11 @@
       <c r="D321" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E321" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>188</v>
       </c>
@@ -7215,8 +11096,11 @@
       <c r="D322" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E322" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>188</v>
       </c>
@@ -7229,8 +11113,14 @@
       <c r="D323" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E323" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F323" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>188</v>
       </c>
@@ -7243,8 +11133,14 @@
       <c r="D324" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E324" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F324" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>188</v>
       </c>
@@ -7257,8 +11153,14 @@
       <c r="D325" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E325" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F325" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>188</v>
       </c>
@@ -7271,8 +11173,14 @@
       <c r="D326" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E326" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F326" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>2</v>
       </c>
@@ -7285,8 +11193,14 @@
       <c r="D327" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E327" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F327" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>2</v>
       </c>
@@ -7299,8 +11213,14 @@
       <c r="D328" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E328" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F328" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>2</v>
       </c>
@@ -7313,8 +11233,14 @@
       <c r="D329" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E329" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F329" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>2</v>
       </c>
@@ -7327,8 +11253,14 @@
       <c r="D330" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E330" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F330" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>2</v>
       </c>
@@ -7341,8 +11273,11 @@
       <c r="D331" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E331" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>2</v>
       </c>
@@ -7355,8 +11290,11 @@
       <c r="D332" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E332" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>2</v>
       </c>
@@ -7369,8 +11307,11 @@
       <c r="D333" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E333" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>2</v>
       </c>
@@ -7383,8 +11324,14 @@
       <c r="D334" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E334" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F334" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>2</v>
       </c>
@@ -7397,8 +11344,14 @@
       <c r="D335" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E335" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F335" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>2</v>
       </c>
@@ -7411,8 +11364,14 @@
       <c r="D336" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E336" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F336" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>2</v>
       </c>
@@ -7425,8 +11384,11 @@
       <c r="D337" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E337" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>2</v>
       </c>
@@ -7439,8 +11401,11 @@
       <c r="D338" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E338" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>2</v>
       </c>
@@ -7453,8 +11418,14 @@
       <c r="D339" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E339" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F339" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>2</v>
       </c>
@@ -7467,8 +11438,14 @@
       <c r="D340" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E340" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F340" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>2</v>
       </c>
@@ -7481,8 +11458,11 @@
       <c r="D341" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E341" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>2</v>
       </c>
@@ -7495,8 +11475,11 @@
       <c r="D342" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E342" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>2</v>
       </c>
@@ -7509,8 +11492,14 @@
       <c r="D343" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E343" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F343" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>2</v>
       </c>
@@ -7523,8 +11512,14 @@
       <c r="D344" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E344" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F344" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>2</v>
       </c>
@@ -7537,8 +11532,14 @@
       <c r="D345" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E345" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F345" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>2</v>
       </c>
@@ -7551,8 +11552,14 @@
       <c r="D346" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E346" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F346" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>2</v>
       </c>
@@ -7565,8 +11572,14 @@
       <c r="D347" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E347" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F347" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>2</v>
       </c>
@@ -7579,8 +11592,14 @@
       <c r="D348" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E348" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F348" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>2</v>
       </c>
@@ -7593,8 +11612,14 @@
       <c r="D349" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E349" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F349" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>2</v>
       </c>
@@ -7607,8 +11632,14 @@
       <c r="D350" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E350" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F350" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>2</v>
       </c>
@@ -7621,8 +11652,11 @@
       <c r="D351" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E351" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>2</v>
       </c>
@@ -7635,8 +11669,11 @@
       <c r="D352" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E352" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>2</v>
       </c>
@@ -7649,8 +11686,11 @@
       <c r="D353" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E353" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>2</v>
       </c>
@@ -7663,8 +11703,14 @@
       <c r="D354" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E354" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F354" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>2</v>
       </c>
@@ -7677,8 +11723,14 @@
       <c r="D355" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E355" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F355" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>2</v>
       </c>
@@ -7691,8 +11743,14 @@
       <c r="D356" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E356" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F356" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>17</v>
       </c>
@@ -7705,8 +11763,14 @@
       <c r="D357" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E357" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F357" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>17</v>
       </c>
@@ -7719,8 +11783,14 @@
       <c r="D358" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E358" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F358" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>17</v>
       </c>
@@ -7733,8 +11803,14 @@
       <c r="D359" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E359" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F359" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>17</v>
       </c>
@@ -7747,8 +11823,14 @@
       <c r="D360" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E360" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F360" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>17</v>
       </c>
@@ -7761,8 +11843,14 @@
       <c r="D361" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E361" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F361" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>17</v>
       </c>
@@ -7775,8 +11863,11 @@
       <c r="D362" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E362" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>17</v>
       </c>
@@ -7789,8 +11880,14 @@
       <c r="D363" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E363" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F363" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>17</v>
       </c>
@@ -7803,8 +11900,11 @@
       <c r="D364" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E364" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>17</v>
       </c>
@@ -7817,8 +11917,14 @@
       <c r="D365" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E365" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F365" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>17</v>
       </c>
@@ -7831,8 +11937,14 @@
       <c r="D366" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E366" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F366" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>17</v>
       </c>
@@ -7845,8 +11957,14 @@
       <c r="D367" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E367" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F367" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>17</v>
       </c>
@@ -7859,8 +11977,14 @@
       <c r="D368" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E368" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F368" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>17</v>
       </c>
@@ -7873,8 +11997,14 @@
       <c r="D369" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E369" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F369" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>17</v>
       </c>
@@ -7887,8 +12017,14 @@
       <c r="D370" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E370" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F370" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>17</v>
       </c>
@@ -7901,8 +12037,14 @@
       <c r="D371" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E371" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F371" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>17</v>
       </c>
@@ -7915,9 +12057,15 @@
       <c r="D372" t="s">
         <v>732</v>
       </c>
+      <c r="E372" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F372" t="s">
+        <v>1453</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D372" xr:uid="{6A3A076C-ECA7-4854-BDDC-C813E3A40233}"/>
+  <autoFilter ref="A1:F372" xr:uid="{6A3A076C-ECA7-4854-BDDC-C813E3A40233}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>